--- a/test/results/model_comparison/comparison.xlsx
+++ b/test/results/model_comparison/comparison.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leven\PycharmProjects\jogi-agent-clean\test\results\model_comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD10EBCB-C96B-4604-8F22-6FF91D5ADF3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06E77C3-B8F7-4596-AB18-4E2EBF991AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
   </bookViews>
@@ -131,6 +131,5324 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-UM"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Feuil1!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Faithfulness</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Base Model</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base Model without Verifier</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unified Model without Verifier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$2:$E$2</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.97204699999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98533300000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98601099999999997</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99102999999999997</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B004-405D-9E97-E2372F849558}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="523607375"/>
+        <c:axId val="522801679"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="523607375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522801679"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="522801679"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="523607375"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-UM"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>Hallutination</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-UM"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Base Model</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base Model without Verifier</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unified Model without Verifier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$3:$E$3</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>2.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.47E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.9999999999999993E-3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6A89-462B-82BF-D1772347A3EB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="358590895"/>
+        <c:axId val="522845359"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="358590895"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522845359"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="522845359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="358590895"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-UM"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>Answer Relevancy</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-UM"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Base Model</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base Model without Verifier</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unified Model without Verifier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$4:$E$4</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.98721400000000004</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.96231800000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.98141299999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.98063500000000003</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0F1C-46E1-A123-1ECE06C6A3DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="551532991"/>
+        <c:axId val="522842959"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="551532991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522842959"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="522842959"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="551532991"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-UM"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>Context Relevancy</a:t>
+            </a:r>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-UM"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Base Model</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base Model without Verifier</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unified Model without Verifier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$5:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>0.96666700000000005</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.908667</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88471</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.973333</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97C9-471D-AD2F-9FD690772695}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="549981167"/>
+        <c:axId val="522792559"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="549981167"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522792559"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="522792559"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="549981167"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-UM"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="de-DE"/>
+              <a:t>T</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>otal</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU" baseline="0"/>
+              <a:t> Tokens avg.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-UM"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Base Model</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base Model without Verifier</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unified Model without Verifier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$6:$E$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16870.72</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10250.719999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16484.48</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>10966.28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8118-4029-B2F2-3BBD6C9DE0EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="541801807"/>
+        <c:axId val="522800719"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="541801807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522800719"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="522800719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="541801807"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-UM"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="fr-FR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>Runtime</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU" baseline="0"/>
+              <a:t> avg.</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-UM"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>Base Model</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Base Model without Verifier</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Unified Model without Verifier</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Feuil1!$B$7:$E$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>23.34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>18.27</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20.14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6355-4C76-B588-6B2ACBDF2430}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="182"/>
+        <c:axId val="446690367"/>
+        <c:axId val="522812239"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="446690367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="522812239"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="522812239"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-UM"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="446690367"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-UM"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Graphique 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEB105F2-07E3-3C30-9C77-3F0895B0F788}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Graphique 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{598A3C0E-276D-DF02-7619-6C2DF81830B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1019175</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Graphique 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D00E275E-12F8-703E-233F-14789AA9E170}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1009650</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Graphique 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3189DD40-2F1A-5794-B506-731B43C94B55}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Graphique 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3F38702B-6B87-F99C-310A-D8602F9AC812}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Graphique 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1213FE35-ED9E-8B4F-94AA-E39423629169}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,5 +6001,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/test/results/model_comparison/comparison.xlsx
+++ b/test/results/model_comparison/comparison.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leven\PycharmProjects\jogi-agent-clean\test\results\model_comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06E77C3-B8F7-4596-AB18-4E2EBF991AB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF84642-2C52-4042-89B4-B8516CBA0811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Összefoglaló" sheetId="1" r:id="rId1"/>
+    <sheet name="Kérdések" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="52">
   <si>
     <t>Base Model</t>
   </si>
@@ -79,11 +80,131 @@
   <si>
     <t>Mérés 25 kérdésen történt, csoportonként 3 könnyű, 2 nehéz kérdésen, illetve plusz 5 kombinált kérdésen.</t>
   </si>
+  <si>
+    <t>GDPR rendelet</t>
+  </si>
+  <si>
+    <t>SZJA törvény</t>
+  </si>
+  <si>
+    <t>Kombinált</t>
+  </si>
+  <si>
+    <t>könnyű</t>
+  </si>
+  <si>
+    <t>nehéz</t>
+  </si>
+  <si>
+    <t>összetett</t>
+  </si>
+  <si>
+    <t>Munkavállalóként hány munkanap távollétre vagyok jogosult a hozzátartozóm halála esetén a Munka Törvénykönyve alapján?</t>
+  </si>
+  <si>
+    <t>Legalább hány nappal korábban köteles a munkavállaló írásban bejelenteni a fizetés nélküli szabadság igénybevételét a munkáltatója felé?</t>
+  </si>
+  <si>
+    <t>A munkavállaló súlyos egészségi okból gondozásra szoruló hozzátartozója ápolása céljából évente legfeljebb hány munkanap mentesülésre jogosult a munkavégzési kötelezettsége alól?</t>
+  </si>
+  <si>
+    <t>A felügyeleti hatóság korrekciós hatáskörében eljárva milyen intézkedést hozhat, ha egy adatkezelő adatkezelési tevékenysége megsértette a rendelet rendelkezéseit?</t>
+  </si>
+  <si>
+    <t>Mentesülhet-e az adatkezelő a kártérítési felelősség alól, ha bizonyítani tudja, hogy a kárt előidéző eseményért őt semmilyen módon nem terheli felelősség?</t>
+  </si>
+  <si>
+    <t>Munka Törvénykönyve (Mt,)</t>
+  </si>
+  <si>
+    <t>Egy vállalat átalakulása során (munkáltató személyében bekövetkező változás) az átadó munkáltatónál üzemi tanács nem működik, A munkáltatók megállapodtak, hogy az átvevő munkáltató tájékoztatja a munkavállalókat az átszállásról, Az átvevő munkáltató az átszállás napján írásban közölte a munkáltató azonosító adatait és a munkafeltételek változását, Milyen jogi következménye van annak, hogy a tájékoztatásra az átszállást megelőző 15 napos határidőn belül nem került sor, és milyen felelősségi szabály vonatkozik az átszállás előtti munkavállalói követelésekre?</t>
+  </si>
+  <si>
+    <t>Egy munkavállaló, aki megváltozott munkaképességű, július 1-jén lépett munkaviszonyba, A munkavállaló augusztus hónapban üzemi baleset miatt vált keresőképtelenné, majd a felépülése után, októberben betegség miatt 10 munkanapra keresőképtelenné vált, Jogosult-e az érintett a 120, § szerinti 5 munkanap pótszabadságra az adott naptári évben, és hány munkanap betegszabadság illeti meg az év hátralévő részében a 126, § szabályai alapján?</t>
+  </si>
+  <si>
+    <t>Egy ügyfél vagyoni kárt szenvedett az adatkezelő szabálytalan adatkezelése miatt, Melyik cikk alapján jogosult kártérítést követelni az adatkezelőtől?</t>
+  </si>
+  <si>
+    <t>Egy ügyvédi iroda (adatkezelő) szakmai titoktartási kötelezettség hatálya alá tartozó iratanyagot kezel, A felügyeleti hatóság vizsgálatot indít az irodánál, és betekintést kér az ügyfélaktákba, Hogyan kell a tagállami jog szerinti titoktartási kötelezettséget a 90, cikk alapján összeegyeztetni a felügyeleti hatóság 58, cikk szerinti ellenőrzési hatáskörével, és milyen feltételeknek kell megfelelni ahhoz, hogy a hatóság egyáltalán korlátozhatja az adatkezelőre vonatkozó titoktartási kötelezettséget?</t>
+  </si>
+  <si>
+    <t>Egy érintett a 18, cikk (1) bekezdésének c) pontjára hivatkozva kéri személyes adatai kezelésének korlátozását, mivel az adatkezelőnek a konkrét adatkezelési cél megvalósulása miatt már nincs szüksége az adatokra, de az érintett azokat egy folyamatban lévő polgári peres eljárásban bizonyítékként kívánja felhasználni, Az adatkezelő az adatokat a korlátozást követően egy külső, jogi képviseletet ellátó ügyvédi iroda szerverére kívánja áthelyezni jogi igényeinek védelme érdekében, Megfelel-e ez az adatkezelési művelet a 18, cikk (2) bekezdésének, és milyen tájékoztatási kötelezettségei keletkeznek az adatkezelőnek az adatkezelés esetleges későbbi feloldása kapcsán?</t>
+  </si>
+  <si>
+    <t>Polgári Törvénykönyv (Ptk,)</t>
+  </si>
+  <si>
+    <t>Házastársak elváltak, de nem tudnak megállapodni a közös lakás további használatáról, Melyik szerv dönthet ilyen esetben a lakáshasználat rendezéséről valamelyik fél kérelmére?</t>
+  </si>
+  <si>
+    <t>Egy bank hitelt nyújtott, amelynek biztosítékául két zálogjogosult is bejegyeztetett zálogjogot, Átveheti-e a megelőző ranghelyű zálogjogosult a zálogjog érvényesítését a már megkezdett eljárás során?</t>
+  </si>
+  <si>
+    <t>A vagyonrendelő és a kedvezményezett elégedetlen a vagyonkezelő döntéseivel, ezért írásban utasítják a vagyonkezelőt a kezelt vagyon értékesítésére, Érvényes-e ez az utasítás?</t>
+  </si>
+  <si>
+    <t>Egy határozatlan idejű bérleti szerződés esetén a bérbeadó a hónap 20, napján közli a rendes felmondást a bérlővel, A Ptk, 6:347, § alapján a bérleti jogviszony mikor tekinthető megszűntnek, tekintettel arra, hogy a felek nem a törvényben meghatározott 15, napi határidőt tartották be?</t>
+  </si>
+  <si>
+    <t>Egy vétőképtelen személy kárt okoz egy harmadik félnek, A kártérítési perben a vétőképtelen gondozója bizonyítja, hogy a károkozás idején a felügyeletet megfelelően ellátta, és a nevelésével kapcsolatban semmilyen felróhatóság nem terheli, A Ptk, 6:544, § rendelkezései értelmében mentesül-e a gondozó a kártérítési felelősség alól, vagy a vétőképtelen személy cselekvőképességének hiánya objektív felelősséget von maga után?</t>
+  </si>
+  <si>
+    <t>Egy magánszemély közüzemi szolgáltatója a fogyasztóvédelmi törvényben meghatározott szabályok szerint elengedett egy tartozást, Milyen jövedelemhatár esetén nem keletkezik ebből adóköteles jövedelme a magánszemélynek, ha a kötelezett és a vele közös háztartásban élő hozzátartozóinak egy főre eső jövedelme a nyilatkozattételt megelőző három hónap átlagában a szociális vetítési alap összegének kétszeresét vizsgáljuk?</t>
+  </si>
+  <si>
+    <t>Az SzJA törvény 50, § (7) bekezdése alapján mennyi időre tilos ismételten átalányadózást választania annak az egyéni vállalkozónak, aki az átalányadózását megszüntette, vagy az arra való jogosultsága megszűnt?</t>
+  </si>
+  <si>
+    <t>A 67/C, § alapján az adóévben kriptoeszközzel végrehajtott ügyletből származó ügyleti bevételt akkor nem kell megállapítani, ha az ügyletből származó bevétel a minimálbér mekkora százalékát nem haladja meg, feltéve, hogy a bevétel megszerzésének napján más, azonos tárgyú ügyletből a magánszemély nem szerez bevételt, továbbá az adóévben e bevételek összege a minimálbért nem haladja meg?</t>
+  </si>
+  <si>
+    <t>Egy magánszemély egyéni vállalkozóként mezőgazdasági tevékenységet folytat, és elhatárolt veszteséggel rendelkezik, A vállalkozó az adóév végén megszünteti egyéni vállalkozói jogállását, és tevékenységét mezőgazdasági őstermelőként folytatja tovább, Milyen szabályok szerint számolhatja el a korábbi egyéni vállalkozói időszakból fennmaradt elhatárolt veszteségét az őstermelői jogállás alatt, figyelembe véve a 49/A, § (10) bekezdés d) pontját?</t>
+  </si>
+  <si>
+    <t>A 66, § (1) bekezdés a) pont ae) és ag) alpontja értelmében osztaléknak minősülő juttatások esetében a 66, § (4) bekezdése értelmében mikor nem alkalmazható az osztalékjövedelemre vonatkozó rendelkezés, ha a kedvezményezett magánszemély a jogállását nem alapítói, hanem egyéb, tevékenységnyújtással összefüggő jogcímen szerezte?</t>
+  </si>
+  <si>
+    <t>Egy munkáltató teljesítménybérezési rendszert vezet be, amelyhez a munkavállalók szigorú KPI-jait egy felhőalapú rendszerben tárolja, Az adatvédelmi tisztviselő (GDPR 37, cikk) aggályokat fogalmaz meg a rendszer adatbiztonsága miatt, ugyanakkor a munkáltató a 138, § szerinti teljesítménykövetelmény-megállapítási kötelezettsége kapcsán vitába keveredik a dolgozókkal, Mely jogszabályi rendelkezések alapján kell a munkáltatónak bizonyítania a rendszer jogszerűségét, és milyen adatvédelmi szankciókat kockáztat, ha a teljesítményértékeléshez egészségügyi adatokat (GDPR 9, cikk) is szisztematikusan rögzít?</t>
+  </si>
+  <si>
+    <t>Egy zálogjogosult (Ptk, 5:131, §) el kívánja árverezni egy adós üzemi berendezését, Az eljárás során a zálogjogosult az adós által a cégtől kapott, kedvezményes lakáscélú hitel (SZJA 72, §) dokumentációját is értékesítené, mint a követeléshez kapcsolódó iratanyagot, Hogyan érinti az előzetes értesítési kötelezettség (Ptk, 5:131, §) az adatkezelési szabályokat, ha az értékesítendő iratok az érintettek különleges adatait (GDPR 9, cikk) tartalmazzák, és a zálogtárgy nem esik a gyorsan romló dolgok körébe?</t>
+  </si>
+  <si>
+    <t>Munkáltatói kártérítési felelősség körébe tartozó hiány esetén a felek megállapodnak, hogy a munkavállaló a tartozását a munkáltató által korábban nyújtott munkabérelőleg (SZJA 72, §) elszámolásával egyenlíti ki, A folyamat során azonban a munkáltató a munkavállaló szabadságmegváltását is beszámítaná a hiányba, Milyen munkajogi korlátok vonatkoznak a szabadság kiadására/megváltására (Mt, 115, §) a kártérítési beszámítás során, és hogyan minősül adózási szempontból a kártérítési felelősséggel összefüggő hiány (SZJA 72, § (4) m) pont)?</t>
+  </si>
+  <si>
+    <t>Egy közfeladatot ellátó szerv (GDPR 37, cikk) zálogjogot érvényesít egy olyan ingatlanon, amelynek a tulajdonosa egyúttal a szervnél munkaviszonyban álló magánszemély, A szerv az értékesítési folyamat során a zálogkötelezett munkavállalói jövedelemadatait is kezeli a követelés mértékének megállapításához, Ütközik-e az SZJA törvény 4, § szerinti bevétel fogalma és a munkabér-elszámolás adatkezelési rendje a Ptk, 5:131, § szerinti előzetes értesítési kötelezettséggel, ha a zálogjogosult a közös adatvédelmi tisztviselő révén kívánja biztosítani az adatok védelmét?</t>
+  </si>
+  <si>
+    <t>Biztosítási szerződés keretében a biztosító a fedezetfeltöltés (Ptk, 6:461, §) elmulasztása miatt csökkenti a biztosítási összeget, ugyanakkor az adóhatóság az eredeti (teljes) biztosítási összeg után megfizetett díj kedvezményezettjének jövedelemadózását vizsgálja, Hogyan értelmezhető az SZJA törvény 72, § szerinti kamatkedvezmény, ha a biztosító a fedezetfeltöltés során kedvezményes törlesztési lehetőséget kínál a munkavállaló szerződő félnek, és hogyan kell biztosítani az adatvédelmi tisztviselő bevonását, ha a biztosítási esemény különleges adatot (GDPR 9, cikk) is érint?</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Law</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Error:</t>
+  </si>
+  <si>
+    <t>Error avg.:</t>
+  </si>
+  <si>
+    <t>Avg.:</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="167" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -101,7 +222,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -109,13 +230,345 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -189,7 +642,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Feuil1!$A$2</c:f>
+              <c:f>Összefoglaló!$A$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -210,7 +663,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:f>Összefoglaló!$B$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -230,7 +683,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil1!$B$2:$E$2</c:f>
+              <c:f>Összefoglaló!$B$2:$E$2</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -510,7 +963,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:f>Összefoglaló!$B$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -530,7 +983,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil1!$B$3:$E$3</c:f>
+              <c:f>Összefoglaló!$B$3:$E$3</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="4"/>
@@ -810,7 +1263,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:f>Összefoglaló!$B$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -830,7 +1283,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil1!$B$4:$E$4</c:f>
+              <c:f>Összefoglaló!$B$4:$E$4</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1092,7 +1545,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-UM"/>
+          <a:endParaRPr lang="de-DE"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1118,7 +1571,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:f>Összefoglaló!$B$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1138,7 +1591,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil1!$B$5:$E$5</c:f>
+              <c:f>Összefoglaló!$B$5:$E$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1433,7 +1886,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:f>Összefoglaló!$B$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1453,7 +1906,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil1!$B$6:$E$6</c:f>
+              <c:f>Összefoglaló!$B$6:$E$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1744,7 +2197,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Feuil1!$B$1:$E$1</c:f>
+              <c:f>Összefoglaló!$B$1:$E$1</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1764,7 +2217,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Feuil1!$B$7:$E$7</c:f>
+              <c:f>Összefoglaló!$B$7:$E$7</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -6003,4 +6456,1473 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36BC549-5F0D-4260-974E-C5029CF103D9}">
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="3"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="4"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="M2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="N2" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="O2" s="20" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1</v>
+      </c>
+      <c r="E3" s="23">
+        <v>1</v>
+      </c>
+      <c r="F3" s="24">
+        <v>1</v>
+      </c>
+      <c r="G3" s="22">
+        <v>1</v>
+      </c>
+      <c r="H3" s="23">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="I3" s="24">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="J3" s="22">
+        <v>1</v>
+      </c>
+      <c r="K3" s="23">
+        <v>1</v>
+      </c>
+      <c r="L3" s="24">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="M3" s="22">
+        <v>1</v>
+      </c>
+      <c r="N3" s="23">
+        <v>0.9375</v>
+      </c>
+      <c r="O3" s="25">
+        <v>0.66666666666666596</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="6">
+        <v>0.76923076923076905</v>
+      </c>
+      <c r="E4" s="7">
+        <v>1</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="J4" s="6">
+        <v>1</v>
+      </c>
+      <c r="K4" s="7">
+        <v>1</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M4" s="6">
+        <v>1</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0.92307692307692302</v>
+      </c>
+      <c r="O4" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.8125</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0.95652173913043403</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0.6</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0.93333333333333302</v>
+      </c>
+      <c r="N5" s="7">
+        <v>1</v>
+      </c>
+      <c r="O5" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <v>0.94444444444444398</v>
+      </c>
+      <c r="F6" s="8">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+      <c r="J6" s="6">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="M6" s="6">
+        <v>1</v>
+      </c>
+      <c r="N6" s="7">
+        <v>1</v>
+      </c>
+      <c r="O6" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="10">
+        <v>1</v>
+      </c>
+      <c r="F7" s="11">
+        <v>1</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="L7" s="11">
+        <v>1</v>
+      </c>
+      <c r="M7" s="9">
+        <v>1</v>
+      </c>
+      <c r="N7" s="10">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="O7" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="22">
+        <v>1</v>
+      </c>
+      <c r="E8" s="23">
+        <v>1</v>
+      </c>
+      <c r="F8" s="24">
+        <v>1</v>
+      </c>
+      <c r="G8" s="22">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="H8" s="23">
+        <v>1</v>
+      </c>
+      <c r="I8" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="J8" s="22">
+        <v>1</v>
+      </c>
+      <c r="K8" s="23">
+        <v>1</v>
+      </c>
+      <c r="L8" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="M8" s="22">
+        <v>1</v>
+      </c>
+      <c r="N8" s="23">
+        <v>1</v>
+      </c>
+      <c r="O8" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="8">
+        <v>1</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+      <c r="J9" s="6">
+        <v>1</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="L9" s="8">
+        <v>1</v>
+      </c>
+      <c r="M9" s="6">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7">
+        <v>0.95833333333333304</v>
+      </c>
+      <c r="O9" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1</v>
+      </c>
+      <c r="I10" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1</v>
+      </c>
+      <c r="K10" s="7">
+        <v>1</v>
+      </c>
+      <c r="L10" s="8">
+        <v>1</v>
+      </c>
+      <c r="M10" s="6">
+        <v>1</v>
+      </c>
+      <c r="N10" s="7">
+        <v>1</v>
+      </c>
+      <c r="O10" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1</v>
+      </c>
+      <c r="I11" s="8">
+        <v>1</v>
+      </c>
+      <c r="J11" s="6">
+        <v>1</v>
+      </c>
+      <c r="K11" s="7">
+        <v>1</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="M11" s="6">
+        <v>1</v>
+      </c>
+      <c r="N11" s="7">
+        <v>1</v>
+      </c>
+      <c r="O11" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="F12" s="11">
+        <v>1</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.95652173913043403</v>
+      </c>
+      <c r="I12" s="11">
+        <v>0.75</v>
+      </c>
+      <c r="J12" s="9">
+        <v>1</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="L12" s="11">
+        <v>1</v>
+      </c>
+      <c r="M12" s="9">
+        <v>1</v>
+      </c>
+      <c r="N12" s="10">
+        <v>1</v>
+      </c>
+      <c r="O12" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="22">
+        <v>1</v>
+      </c>
+      <c r="E13" s="23">
+        <v>1</v>
+      </c>
+      <c r="F13" s="24">
+        <v>1</v>
+      </c>
+      <c r="G13" s="22">
+        <v>1</v>
+      </c>
+      <c r="H13" s="23">
+        <v>1</v>
+      </c>
+      <c r="I13" s="24">
+        <v>1</v>
+      </c>
+      <c r="J13" s="22">
+        <v>1</v>
+      </c>
+      <c r="K13" s="23">
+        <v>1</v>
+      </c>
+      <c r="L13" s="24">
+        <v>1</v>
+      </c>
+      <c r="M13" s="22">
+        <v>1</v>
+      </c>
+      <c r="N13" s="23">
+        <v>1</v>
+      </c>
+      <c r="O13" s="25">
+        <v>0.66666666666666596</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="6">
+        <v>1</v>
+      </c>
+      <c r="K14" s="7">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8">
+        <v>1</v>
+      </c>
+      <c r="M14" s="6">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7">
+        <v>1</v>
+      </c>
+      <c r="O14" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="6">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <v>1</v>
+      </c>
+      <c r="G15" s="6">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1</v>
+      </c>
+      <c r="I15" s="8">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7">
+        <v>1</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="M15" s="6">
+        <v>1</v>
+      </c>
+      <c r="N15" s="7">
+        <v>1</v>
+      </c>
+      <c r="O15" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8">
+        <v>1</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="6">
+        <v>0.90909090909090895</v>
+      </c>
+      <c r="K16" s="7">
+        <v>1</v>
+      </c>
+      <c r="L16" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="M16" s="6">
+        <v>1</v>
+      </c>
+      <c r="N16" s="7">
+        <v>1</v>
+      </c>
+      <c r="O16" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="9">
+        <v>1</v>
+      </c>
+      <c r="E17" s="10">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11">
+        <v>1</v>
+      </c>
+      <c r="G17" s="9">
+        <v>1</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0.95454545454545403</v>
+      </c>
+      <c r="I17" s="11">
+        <v>1</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0.952380952380952</v>
+      </c>
+      <c r="L17" s="11">
+        <v>1</v>
+      </c>
+      <c r="M17" s="9">
+        <v>1</v>
+      </c>
+      <c r="N17" s="10">
+        <v>1</v>
+      </c>
+      <c r="O17" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="22">
+        <v>1</v>
+      </c>
+      <c r="E18" s="23">
+        <v>1</v>
+      </c>
+      <c r="F18" s="24">
+        <v>1</v>
+      </c>
+      <c r="G18" s="22">
+        <v>1</v>
+      </c>
+      <c r="H18" s="23">
+        <v>0.90909090909090895</v>
+      </c>
+      <c r="I18" s="24">
+        <v>1</v>
+      </c>
+      <c r="J18" s="22">
+        <v>1</v>
+      </c>
+      <c r="K18" s="23">
+        <v>0.92307692307692302</v>
+      </c>
+      <c r="L18" s="24">
+        <v>1</v>
+      </c>
+      <c r="M18" s="22">
+        <v>1</v>
+      </c>
+      <c r="N18" s="23">
+        <v>1</v>
+      </c>
+      <c r="O18" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.9375</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0.64285714285714202</v>
+      </c>
+      <c r="I19" s="8">
+        <v>1</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="K19" s="7">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
+        <v>1</v>
+      </c>
+      <c r="M19" s="6">
+        <v>1</v>
+      </c>
+      <c r="N19" s="7">
+        <v>1</v>
+      </c>
+      <c r="O19" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1</v>
+      </c>
+      <c r="F20" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G20" s="6">
+        <v>1</v>
+      </c>
+      <c r="H20" s="7">
+        <v>1</v>
+      </c>
+      <c r="I20" s="8">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="J20" s="6">
+        <v>1</v>
+      </c>
+      <c r="K20" s="7">
+        <v>1</v>
+      </c>
+      <c r="L20" s="8">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="M20" s="6">
+        <v>1</v>
+      </c>
+      <c r="N20" s="7">
+        <v>1</v>
+      </c>
+      <c r="O20" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.94444444444444398</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8">
+        <v>1</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1</v>
+      </c>
+      <c r="I21" s="8">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6">
+        <v>1</v>
+      </c>
+      <c r="K21" s="7">
+        <v>1</v>
+      </c>
+      <c r="L21" s="8">
+        <v>1</v>
+      </c>
+      <c r="M21" s="6">
+        <v>0.90909090909090895</v>
+      </c>
+      <c r="N21" s="7">
+        <v>1</v>
+      </c>
+      <c r="O21" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1</v>
+      </c>
+      <c r="E22" s="10">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11">
+        <v>1</v>
+      </c>
+      <c r="G22" s="9">
+        <v>1</v>
+      </c>
+      <c r="H22" s="10">
+        <v>1</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.8</v>
+      </c>
+      <c r="J22" s="9">
+        <v>1</v>
+      </c>
+      <c r="K22" s="10">
+        <v>1</v>
+      </c>
+      <c r="L22" s="11">
+        <v>1</v>
+      </c>
+      <c r="M22" s="9">
+        <v>0.93333333333333302</v>
+      </c>
+      <c r="N22" s="10">
+        <v>1</v>
+      </c>
+      <c r="O22" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D23" s="22">
+        <v>1</v>
+      </c>
+      <c r="E23" s="23">
+        <v>1</v>
+      </c>
+      <c r="F23" s="24">
+        <v>1</v>
+      </c>
+      <c r="G23" s="22">
+        <v>1</v>
+      </c>
+      <c r="H23" s="23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="24">
+        <v>1</v>
+      </c>
+      <c r="J23" s="22">
+        <v>1</v>
+      </c>
+      <c r="K23" s="23">
+        <v>1</v>
+      </c>
+      <c r="L23" s="24">
+        <v>1</v>
+      </c>
+      <c r="M23" s="22">
+        <v>1</v>
+      </c>
+      <c r="N23" s="23">
+        <v>1</v>
+      </c>
+      <c r="O23" s="25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" s="6">
+        <v>0.86666666666666603</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.95</v>
+      </c>
+      <c r="F24" s="8">
+        <v>1</v>
+      </c>
+      <c r="G24" s="6">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8">
+        <v>1</v>
+      </c>
+      <c r="J24" s="6">
+        <v>1</v>
+      </c>
+      <c r="K24" s="7">
+        <v>1</v>
+      </c>
+      <c r="L24" s="8">
+        <v>1</v>
+      </c>
+      <c r="M24" s="6">
+        <v>1</v>
+      </c>
+      <c r="N24" s="7">
+        <v>0.95454545454545403</v>
+      </c>
+      <c r="O24" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="F25" s="8">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7">
+        <v>1</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1</v>
+      </c>
+      <c r="J25" s="6">
+        <v>1</v>
+      </c>
+      <c r="K25" s="7">
+        <v>1</v>
+      </c>
+      <c r="L25" s="8">
+        <v>1</v>
+      </c>
+      <c r="M25" s="6">
+        <v>1</v>
+      </c>
+      <c r="N25" s="7">
+        <v>1</v>
+      </c>
+      <c r="O25" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1</v>
+      </c>
+      <c r="F26" s="8">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7">
+        <v>1</v>
+      </c>
+      <c r="I26" s="8">
+        <v>1</v>
+      </c>
+      <c r="J26" s="6">
+        <v>1</v>
+      </c>
+      <c r="K26" s="7">
+        <v>1</v>
+      </c>
+      <c r="L26" s="8">
+        <v>0.85714285714285698</v>
+      </c>
+      <c r="M26" s="6">
+        <v>1</v>
+      </c>
+      <c r="N26" s="7">
+        <v>1</v>
+      </c>
+      <c r="O26" s="27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0.86666666666666603</v>
+      </c>
+      <c r="E27" s="10">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11">
+        <v>1</v>
+      </c>
+      <c r="G27" s="9">
+        <v>1</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0.952380952380952</v>
+      </c>
+      <c r="I27" s="11">
+        <v>1</v>
+      </c>
+      <c r="J27" s="9">
+        <v>1</v>
+      </c>
+      <c r="K27" s="10">
+        <v>1</v>
+      </c>
+      <c r="L27" s="11">
+        <v>1</v>
+      </c>
+      <c r="M27" s="9">
+        <v>1</v>
+      </c>
+      <c r="N27" s="10">
+        <v>0.90909090909090895</v>
+      </c>
+      <c r="O27" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28" s="12">
+        <f>AVERAGE(D3:D27)</f>
+        <v>0.97204700854700843</v>
+      </c>
+      <c r="E28" s="13">
+        <f t="shared" ref="E28:O28" si="0">AVERAGE(E3:E27)</f>
+        <v>0.98721431028551765</v>
+      </c>
+      <c r="F28" s="14">
+        <f t="shared" si="0"/>
+        <v>0.96666666666666656</v>
+      </c>
+      <c r="G28" s="12">
+        <f t="shared" si="0"/>
+        <v>0.98533333333333328</v>
+      </c>
+      <c r="H28" s="13">
+        <f t="shared" si="0"/>
+        <v>0.96231846229928053</v>
+      </c>
+      <c r="I28" s="14">
+        <f t="shared" si="0"/>
+        <v>0.90866666666666662</v>
+      </c>
+      <c r="J28" s="12">
+        <f t="shared" si="0"/>
+        <v>0.98601069518716566</v>
+      </c>
+      <c r="K28" s="13">
+        <f t="shared" si="0"/>
+        <v>0.98141251791686568</v>
+      </c>
+      <c r="L28" s="14">
+        <f t="shared" si="0"/>
+        <v>0.88470995670995667</v>
+      </c>
+      <c r="M28" s="12">
+        <f t="shared" si="0"/>
+        <v>0.99103030303030304</v>
+      </c>
+      <c r="N28" s="13">
+        <f t="shared" si="0"/>
+        <v>0.98063519813519806</v>
+      </c>
+      <c r="O28" s="14">
+        <f t="shared" si="0"/>
+        <v>0.97333333333333327</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C29" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="15">
+        <f>25-COUNTIF(D3:D27,1)</f>
+        <v>6</v>
+      </c>
+      <c r="E29" s="16">
+        <f t="shared" ref="E29:F29" si="1">25-COUNTIF(E3:E27,1)</f>
+        <v>6</v>
+      </c>
+      <c r="F29" s="17">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="G29" s="15">
+        <f>25-COUNTIF(G3:G27,1)</f>
+        <v>3</v>
+      </c>
+      <c r="H29" s="16">
+        <f t="shared" ref="H29:I29" si="2">25-COUNTIF(H3:H27,1)</f>
+        <v>8</v>
+      </c>
+      <c r="I29" s="17">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="J29" s="15">
+        <f>25-COUNTIF(J3:J27,1)</f>
+        <v>3</v>
+      </c>
+      <c r="K29" s="16">
+        <f t="shared" ref="K29:L29" si="3">25-COUNTIF(K3:K27,1)</f>
+        <v>6</v>
+      </c>
+      <c r="L29" s="17">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="M29" s="15">
+        <f>25-COUNTIF(M3:M27,1)</f>
+        <v>3</v>
+      </c>
+      <c r="N29" s="16">
+        <f t="shared" ref="N29:O29" si="4">25-COUNTIF(N3:N27,1)</f>
+        <v>6</v>
+      </c>
+      <c r="O29" s="17">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C30" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D30" s="31">
+        <f>AVERAGE(D29:F29)</f>
+        <v>5</v>
+      </c>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="31">
+        <f>AVERAGE(G29:I29)</f>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="H30" s="32"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="31">
+        <f>AVERAGE(J29:L29)</f>
+        <v>6.333333333333333</v>
+      </c>
+      <c r="K30" s="32"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="31">
+        <f>AVERAGE(M29:O29)</f>
+        <v>3.6666666666666665</v>
+      </c>
+      <c r="N30" s="32"/>
+      <c r="O30" s="33"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="M30:O30"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D3:O28">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D28:O28">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D29:O29">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1CBD6AED-E61C-4CA0-8210-5EA7351ABED4}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{1CBD6AED-E61C-4CA0-8210-5EA7351ABED4}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>D29:O29</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/test/results/model_comparison/comparison.xlsx
+++ b/test/results/model_comparison/comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leven\PycharmProjects\jogi-agent-clean\test\results\model_comparison\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Levi\PyCharmProjects\jogi-agent-rag\test\results\model_comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF84642-2C52-4042-89B4-B8516CBA0811}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCDF3A6-DB83-47DD-A0F3-E8B5CD9E8339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
   </bookViews>
   <sheets>
     <sheet name="Összefoglaló" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="54">
   <si>
     <t>Base Model</t>
   </si>
@@ -197,13 +197,19 @@
   <si>
     <t>Avg.:</t>
   </si>
+  <si>
+    <t>Total Tokens</t>
+  </si>
+  <si>
+    <t>Verifier Runs</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -222,7 +228,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -339,28 +345,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thick">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -503,8 +487,52 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -519,9 +547,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -531,47 +582,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normál" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -589,7 +623,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="hu-HU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -875,7 +909,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="hu-HU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1175,7 +1209,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="hu-HU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1482,7 +1516,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="hu-HU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1790,7 +1824,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="hu-HU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2105,7 +2139,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="fr-FR"/>
+  <c:lang val="hu-HU"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2413,6 +2447,299 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="hu-HU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="hu-HU"/>
+              <a:t>Total</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="hu-HU" baseline="0"/>
+              <a:t> Token Usage</a:t>
+            </a:r>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="hu-HU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>(Kérdések!$G$31,Kérdések!$L$31,Kérdések!$P$31,Kérdések!$U$31)</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>421768</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>256268</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>412112</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>274157</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CC5E-4F5B-9422-3AB82BAC8060}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1733285104"/>
+        <c:axId val="1302462640"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1733285104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1302462640"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1302462640"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="hu-HU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1733285104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="hu-HU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2653,6 +2980,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
@@ -5651,6 +6018,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -5904,8 +6774,49 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>66675</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>138113</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Diagram 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9758A447-092E-5138-C443-A1D1C44321F5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-téma">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -6222,15 +7133,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA46300E-0F1F-4949-90ED-4C2BDEB1CA35}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -6244,7 +7155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -6261,7 +7172,7 @@
         <v>0.99102999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -6278,7 +7189,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -6295,7 +7206,7 @@
         <v>0.98063500000000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -6312,7 +7223,7 @@
         <v>0.973333</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -6329,7 +7240,7 @@
         <v>10966.28</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -6346,7 +7257,7 @@
         <v>16.37</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -6363,7 +7274,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -6460,1414 +7371,1933 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36BC549-5F0D-4260-974E-C5029CF103D9}">
-  <dimension ref="A1:O30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U31"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="D1" s="2" t="s">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="D1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="2" t="s">
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="4"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="27"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="18" t="s">
+      <c r="G2" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="J2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="K2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="18" t="s">
+      <c r="L2" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="N2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="O2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="18" t="s">
+      <c r="P2" s="35" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="R2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="S2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="T2" s="11" t="s">
         <v>7</v>
       </c>
+      <c r="U2" s="40" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="22">
-        <v>1</v>
-      </c>
-      <c r="E3" s="23">
-        <v>1</v>
-      </c>
-      <c r="F3" s="24">
-        <v>1</v>
-      </c>
-      <c r="G3" s="22">
-        <v>1</v>
-      </c>
-      <c r="H3" s="23">
+      <c r="D3" s="14">
+        <v>1</v>
+      </c>
+      <c r="E3" s="15">
+        <v>1</v>
+      </c>
+      <c r="F3" s="15">
+        <v>1</v>
+      </c>
+      <c r="G3" s="13">
+        <v>10473</v>
+      </c>
+      <c r="H3" s="12">
+        <v>1</v>
+      </c>
+      <c r="I3" s="14">
+        <v>1</v>
+      </c>
+      <c r="J3" s="15">
         <v>0.94117647058823495</v>
       </c>
-      <c r="I3" s="24">
+      <c r="K3" s="16">
         <v>0.66666666666666596</v>
       </c>
-      <c r="J3" s="22">
-        <v>1</v>
-      </c>
-      <c r="K3" s="23">
-        <v>1</v>
-      </c>
-      <c r="L3" s="24">
+      <c r="L3" s="12">
+        <v>7354</v>
+      </c>
+      <c r="M3" s="14">
+        <v>1</v>
+      </c>
+      <c r="N3" s="15">
+        <v>1</v>
+      </c>
+      <c r="O3" s="16">
         <v>0.66666666666666596</v>
       </c>
-      <c r="M3" s="22">
-        <v>1</v>
-      </c>
-      <c r="N3" s="23">
+      <c r="P3" s="11">
+        <v>11434</v>
+      </c>
+      <c r="Q3" s="12">
+        <v>1</v>
+      </c>
+      <c r="R3" s="14">
+        <v>1</v>
+      </c>
+      <c r="S3" s="15">
         <v>0.9375</v>
       </c>
-      <c r="O3" s="25">
+      <c r="T3" s="17">
         <v>0.66666666666666596</v>
       </c>
+      <c r="U3" s="12">
+        <v>8785</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="2">
         <v>0.76923076923076905</v>
       </c>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="8">
+      <c r="E4" s="34">
+        <v>1</v>
+      </c>
+      <c r="F4" s="34">
         <v>0.75</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="18">
+        <v>19524</v>
+      </c>
+      <c r="H4" s="32">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2">
         <v>0.91666666666666596</v>
       </c>
-      <c r="H4" s="7">
-        <v>1</v>
-      </c>
-      <c r="I4" s="8">
+      <c r="J4" s="34">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="J4" s="6">
-        <v>1</v>
-      </c>
-      <c r="K4" s="7">
-        <v>1</v>
-      </c>
-      <c r="L4" s="8">
+      <c r="L4" s="32">
+        <v>8567</v>
+      </c>
+      <c r="M4" s="2">
+        <v>1</v>
+      </c>
+      <c r="N4" s="34">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3">
         <v>0.5</v>
       </c>
-      <c r="M4" s="6">
-        <v>1</v>
-      </c>
-      <c r="N4" s="7">
+      <c r="P4" s="31">
+        <v>12488</v>
+      </c>
+      <c r="Q4" s="32">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2">
+        <v>1</v>
+      </c>
+      <c r="S4" s="34">
         <v>0.92307692307692302</v>
       </c>
-      <c r="O4" s="27">
-        <v>1</v>
+      <c r="T4" s="19">
+        <v>1</v>
+      </c>
+      <c r="U4" s="32">
+        <v>9699</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="7">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="34">
+        <v>1</v>
+      </c>
+      <c r="F5" s="34">
         <v>0.66666666666666596</v>
       </c>
-      <c r="G5" s="6">
-        <v>1</v>
-      </c>
-      <c r="H5" s="7">
+      <c r="G5" s="18">
+        <v>12292</v>
+      </c>
+      <c r="H5" s="32">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="34">
         <v>0.8125</v>
       </c>
-      <c r="I5" s="8">
+      <c r="K5" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="J5" s="6">
-        <v>1</v>
-      </c>
-      <c r="K5" s="7">
+      <c r="L5" s="32">
+        <v>8882</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1</v>
+      </c>
+      <c r="N5" s="34">
         <v>0.95652173913043403</v>
       </c>
-      <c r="L5" s="8">
+      <c r="O5" s="3">
         <v>0.6</v>
       </c>
-      <c r="M5" s="6">
+      <c r="P5" s="31">
+        <v>15949</v>
+      </c>
+      <c r="Q5" s="32">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2">
         <v>0.93333333333333302</v>
       </c>
-      <c r="N5" s="7">
-        <v>1</v>
-      </c>
-      <c r="O5" s="27">
-        <v>1</v>
+      <c r="S5" s="34">
+        <v>1</v>
+      </c>
+      <c r="T5" s="19">
+        <v>1</v>
+      </c>
+      <c r="U5" s="32">
+        <v>8315</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="6">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="34">
         <v>0.94444444444444398</v>
       </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8">
-        <v>1</v>
-      </c>
-      <c r="J6" s="6">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
-        <v>1</v>
-      </c>
-      <c r="L6" s="8">
+      <c r="F6" s="34">
+        <v>1</v>
+      </c>
+      <c r="G6" s="18">
+        <v>13206</v>
+      </c>
+      <c r="H6" s="32">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="34">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+      <c r="L6" s="32">
+        <v>10926</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1</v>
+      </c>
+      <c r="N6" s="34">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3">
         <v>0.8</v>
       </c>
-      <c r="M6" s="6">
-        <v>1</v>
-      </c>
-      <c r="N6" s="7">
-        <v>1</v>
-      </c>
-      <c r="O6" s="27">
-        <v>1</v>
+      <c r="P6" s="31">
+        <v>15433</v>
+      </c>
+      <c r="Q6" s="32">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2">
+        <v>1</v>
+      </c>
+      <c r="S6" s="34">
+        <v>1</v>
+      </c>
+      <c r="T6" s="19">
+        <v>1</v>
+      </c>
+      <c r="U6" s="32">
+        <v>11617</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="28" t="s">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="9">
-        <v>1</v>
-      </c>
-      <c r="E7" s="10">
-        <v>1</v>
-      </c>
-      <c r="F7" s="11">
-        <v>1</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1</v>
-      </c>
-      <c r="H7" s="10">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9">
-        <v>1</v>
-      </c>
-      <c r="K7" s="10">
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="20">
+        <v>13709</v>
+      </c>
+      <c r="H7" s="42">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1</v>
+      </c>
+      <c r="L7" s="42">
+        <v>10360</v>
+      </c>
+      <c r="M7" s="4">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5">
         <v>0.92</v>
       </c>
-      <c r="L7" s="11">
-        <v>1</v>
-      </c>
-      <c r="M7" s="9">
-        <v>1</v>
-      </c>
-      <c r="N7" s="10">
+      <c r="O7" s="6">
+        <v>1</v>
+      </c>
+      <c r="P7" s="21">
+        <v>21275</v>
+      </c>
+      <c r="Q7" s="42">
+        <v>2</v>
+      </c>
+      <c r="R7" s="4">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
         <v>0.83333333333333304</v>
       </c>
-      <c r="O7" s="30">
-        <v>1</v>
+      <c r="T7" s="22">
+        <v>1</v>
+      </c>
+      <c r="U7" s="42">
+        <v>9958</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="21" t="s">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="22">
-        <v>1</v>
-      </c>
-      <c r="E8" s="23">
-        <v>1</v>
-      </c>
-      <c r="F8" s="24">
-        <v>1</v>
-      </c>
-      <c r="G8" s="22">
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13">
+        <v>13800</v>
+      </c>
+      <c r="H8" s="12">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14">
         <v>0.91666666666666596</v>
       </c>
-      <c r="H8" s="23">
-        <v>1</v>
-      </c>
-      <c r="I8" s="24">
+      <c r="J8" s="15">
+        <v>1</v>
+      </c>
+      <c r="K8" s="16">
         <v>0.75</v>
       </c>
-      <c r="J8" s="22">
-        <v>1</v>
-      </c>
-      <c r="K8" s="23">
-        <v>1</v>
-      </c>
-      <c r="L8" s="24">
+      <c r="L8" s="12">
+        <v>8846</v>
+      </c>
+      <c r="M8" s="14">
+        <v>1</v>
+      </c>
+      <c r="N8" s="15">
+        <v>1</v>
+      </c>
+      <c r="O8" s="16">
         <v>0.75</v>
       </c>
-      <c r="M8" s="22">
-        <v>1</v>
-      </c>
-      <c r="N8" s="23">
-        <v>1</v>
-      </c>
-      <c r="O8" s="25">
-        <v>1</v>
+      <c r="P8" s="11">
+        <v>13523</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>1</v>
+      </c>
+      <c r="R8" s="14">
+        <v>1</v>
+      </c>
+      <c r="S8" s="15">
+        <v>1</v>
+      </c>
+      <c r="T8" s="17">
+        <v>1</v>
+      </c>
+      <c r="U8" s="12">
+        <v>9696</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34">
         <v>0.95</v>
       </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6">
-        <v>1</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8">
-        <v>1</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1</v>
-      </c>
-      <c r="K9" s="7">
+      <c r="F9" s="34">
+        <v>1</v>
+      </c>
+      <c r="G9" s="18">
+        <v>17389</v>
+      </c>
+      <c r="H9" s="32">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="34">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1</v>
+      </c>
+      <c r="L9" s="32">
+        <v>14124</v>
+      </c>
+      <c r="M9" s="2">
+        <v>1</v>
+      </c>
+      <c r="N9" s="34">
         <v>0.83333333333333304</v>
       </c>
-      <c r="L9" s="8">
-        <v>1</v>
-      </c>
-      <c r="M9" s="6">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7">
+      <c r="O9" s="3">
+        <v>1</v>
+      </c>
+      <c r="P9" s="31">
+        <v>19615</v>
+      </c>
+      <c r="Q9" s="32">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2">
+        <v>1</v>
+      </c>
+      <c r="S9" s="34">
         <v>0.95833333333333304</v>
       </c>
-      <c r="O9" s="27">
-        <v>1</v>
+      <c r="T9" s="19">
+        <v>1</v>
+      </c>
+      <c r="U9" s="32">
+        <v>11901</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="26" t="s">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="6">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1</v>
-      </c>
-      <c r="I10" s="8">
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="34">
+        <v>1</v>
+      </c>
+      <c r="F10" s="34">
+        <v>1</v>
+      </c>
+      <c r="G10" s="18">
+        <v>16060</v>
+      </c>
+      <c r="H10" s="32">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="34">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
         <v>0.75</v>
       </c>
-      <c r="J10" s="6">
-        <v>1</v>
-      </c>
-      <c r="K10" s="7">
-        <v>1</v>
-      </c>
-      <c r="L10" s="8">
-        <v>1</v>
-      </c>
-      <c r="M10" s="6">
-        <v>1</v>
-      </c>
-      <c r="N10" s="7">
-        <v>1</v>
-      </c>
-      <c r="O10" s="27">
-        <v>1</v>
+      <c r="L10" s="32">
+        <v>10520</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1</v>
+      </c>
+      <c r="N10" s="34">
+        <v>1</v>
+      </c>
+      <c r="O10" s="3">
+        <v>1</v>
+      </c>
+      <c r="P10" s="31">
+        <v>15794</v>
+      </c>
+      <c r="Q10" s="32">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1</v>
+      </c>
+      <c r="S10" s="34">
+        <v>1</v>
+      </c>
+      <c r="T10" s="19">
+        <v>1</v>
+      </c>
+      <c r="U10" s="32">
+        <v>10610</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="6">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1</v>
-      </c>
-      <c r="I11" s="8">
-        <v>1</v>
-      </c>
-      <c r="J11" s="6">
-        <v>1</v>
-      </c>
-      <c r="K11" s="7">
-        <v>1</v>
-      </c>
-      <c r="L11" s="8">
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="34">
+        <v>1</v>
+      </c>
+      <c r="F11" s="34">
+        <v>1</v>
+      </c>
+      <c r="G11" s="18">
+        <v>17608</v>
+      </c>
+      <c r="H11" s="32">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="34">
+        <v>1</v>
+      </c>
+      <c r="K11" s="3">
+        <v>1</v>
+      </c>
+      <c r="L11" s="32">
+        <v>11456</v>
+      </c>
+      <c r="M11" s="2">
+        <v>1</v>
+      </c>
+      <c r="N11" s="34">
+        <v>1</v>
+      </c>
+      <c r="O11" s="3">
         <v>0.8</v>
       </c>
-      <c r="M11" s="6">
-        <v>1</v>
-      </c>
-      <c r="N11" s="7">
-        <v>1</v>
-      </c>
-      <c r="O11" s="27">
-        <v>1</v>
+      <c r="P11" s="31">
+        <v>16891</v>
+      </c>
+      <c r="Q11" s="32">
+        <v>1</v>
+      </c>
+      <c r="R11" s="2">
+        <v>1</v>
+      </c>
+      <c r="S11" s="34">
+        <v>1</v>
+      </c>
+      <c r="T11" s="19">
+        <v>1</v>
+      </c>
+      <c r="U11" s="32">
+        <v>16027</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="9">
-        <v>1</v>
-      </c>
-      <c r="E12" s="10">
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
         <v>0.94736842105263097</v>
       </c>
-      <c r="F12" s="11">
-        <v>1</v>
-      </c>
-      <c r="G12" s="9">
-        <v>1</v>
-      </c>
-      <c r="H12" s="10">
+      <c r="F12" s="5">
+        <v>1</v>
+      </c>
+      <c r="G12" s="20">
+        <v>26389</v>
+      </c>
+      <c r="H12" s="42">
+        <v>2</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5">
         <v>0.95652173913043403</v>
       </c>
-      <c r="I12" s="11">
+      <c r="K12" s="6">
         <v>0.75</v>
       </c>
-      <c r="J12" s="9">
-        <v>1</v>
-      </c>
-      <c r="K12" s="10">
+      <c r="L12" s="42">
+        <v>10454</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+      <c r="N12" s="5">
         <v>0.95</v>
       </c>
-      <c r="L12" s="11">
-        <v>1</v>
-      </c>
-      <c r="M12" s="9">
-        <v>1</v>
-      </c>
-      <c r="N12" s="10">
-        <v>1</v>
-      </c>
-      <c r="O12" s="30">
-        <v>1</v>
+      <c r="O12" s="6">
+        <v>1</v>
+      </c>
+      <c r="P12" s="21">
+        <v>15280</v>
+      </c>
+      <c r="Q12" s="42">
+        <v>1</v>
+      </c>
+      <c r="R12" s="4">
+        <v>1</v>
+      </c>
+      <c r="S12" s="5">
+        <v>1</v>
+      </c>
+      <c r="T12" s="22">
+        <v>1</v>
+      </c>
+      <c r="U12" s="42">
+        <v>10015</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="22">
-        <v>1</v>
-      </c>
-      <c r="E13" s="23">
-        <v>1</v>
-      </c>
-      <c r="F13" s="24">
-        <v>1</v>
-      </c>
-      <c r="G13" s="22">
-        <v>1</v>
-      </c>
-      <c r="H13" s="23">
-        <v>1</v>
-      </c>
-      <c r="I13" s="24">
-        <v>1</v>
-      </c>
-      <c r="J13" s="22">
-        <v>1</v>
-      </c>
-      <c r="K13" s="23">
-        <v>1</v>
-      </c>
-      <c r="L13" s="24">
-        <v>1</v>
-      </c>
-      <c r="M13" s="22">
-        <v>1</v>
-      </c>
-      <c r="N13" s="23">
-        <v>1</v>
-      </c>
-      <c r="O13" s="25">
+      <c r="D13" s="14">
+        <v>1</v>
+      </c>
+      <c r="E13" s="15">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13">
+        <v>12921</v>
+      </c>
+      <c r="H13" s="12">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14">
+        <v>1</v>
+      </c>
+      <c r="J13" s="15">
+        <v>1</v>
+      </c>
+      <c r="K13" s="16">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12">
+        <v>9778</v>
+      </c>
+      <c r="M13" s="14">
+        <v>1</v>
+      </c>
+      <c r="N13" s="15">
+        <v>1</v>
+      </c>
+      <c r="O13" s="16">
+        <v>1</v>
+      </c>
+      <c r="P13" s="11">
+        <v>15620</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>1</v>
+      </c>
+      <c r="R13" s="14">
+        <v>1</v>
+      </c>
+      <c r="S13" s="15">
+        <v>1</v>
+      </c>
+      <c r="T13" s="17">
         <v>0.66666666666666596</v>
       </c>
+      <c r="U13" s="12">
+        <v>12082</v>
+      </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="26" t="s">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1</v>
-      </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-      <c r="G14" s="6">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7">
-        <v>1</v>
-      </c>
-      <c r="I14" s="8">
-        <v>1</v>
-      </c>
-      <c r="J14" s="6">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7">
-        <v>1</v>
-      </c>
-      <c r="L14" s="8">
-        <v>1</v>
-      </c>
-      <c r="M14" s="6">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7">
-        <v>1</v>
-      </c>
-      <c r="O14" s="27">
-        <v>1</v>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="34">
+        <v>1</v>
+      </c>
+      <c r="F14" s="34">
+        <v>1</v>
+      </c>
+      <c r="G14" s="18">
+        <v>25681</v>
+      </c>
+      <c r="H14" s="32">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2">
+        <v>1</v>
+      </c>
+      <c r="J14" s="34">
+        <v>1</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="32">
+        <v>9586</v>
+      </c>
+      <c r="M14" s="2">
+        <v>1</v>
+      </c>
+      <c r="N14" s="34">
+        <v>1</v>
+      </c>
+      <c r="O14" s="3">
+        <v>1</v>
+      </c>
+      <c r="P14" s="31">
+        <v>15989</v>
+      </c>
+      <c r="Q14" s="32">
+        <v>1</v>
+      </c>
+      <c r="R14" s="2">
+        <v>1</v>
+      </c>
+      <c r="S14" s="34">
+        <v>1</v>
+      </c>
+      <c r="T14" s="19">
+        <v>1</v>
+      </c>
+      <c r="U14" s="32">
+        <v>10980</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-      <c r="G15" s="6">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7">
-        <v>1</v>
-      </c>
-      <c r="I15" s="8">
-        <v>1</v>
-      </c>
-      <c r="J15" s="6">
-        <v>1</v>
-      </c>
-      <c r="K15" s="7">
-        <v>1</v>
-      </c>
-      <c r="L15" s="8">
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="34">
+        <v>1</v>
+      </c>
+      <c r="F15" s="34">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18">
+        <v>23739</v>
+      </c>
+      <c r="H15" s="32">
+        <v>2</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="34">
+        <v>1</v>
+      </c>
+      <c r="K15" s="3">
+        <v>1</v>
+      </c>
+      <c r="L15" s="32">
+        <v>11563</v>
+      </c>
+      <c r="M15" s="2">
+        <v>1</v>
+      </c>
+      <c r="N15" s="34">
+        <v>1</v>
+      </c>
+      <c r="O15" s="3">
         <v>0.72727272727272696</v>
       </c>
-      <c r="M15" s="6">
-        <v>1</v>
-      </c>
-      <c r="N15" s="7">
-        <v>1</v>
-      </c>
-      <c r="O15" s="27">
-        <v>1</v>
+      <c r="P15" s="31">
+        <v>18430</v>
+      </c>
+      <c r="Q15" s="32">
+        <v>1</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+      <c r="S15" s="34">
+        <v>1</v>
+      </c>
+      <c r="T15" s="19">
+        <v>1</v>
+      </c>
+      <c r="U15" s="32">
+        <v>11137</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="26" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="6">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8">
-        <v>1</v>
-      </c>
-      <c r="G16" s="6">
+      <c r="D16" s="2">
+        <v>1</v>
+      </c>
+      <c r="E16" s="34">
+        <v>1</v>
+      </c>
+      <c r="F16" s="34">
+        <v>1</v>
+      </c>
+      <c r="G16" s="18">
+        <v>12286</v>
+      </c>
+      <c r="H16" s="32">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2">
         <v>0.8</v>
       </c>
-      <c r="H16" s="7">
+      <c r="J16" s="34">
         <v>0.88888888888888795</v>
       </c>
-      <c r="I16" s="8">
-        <v>1</v>
-      </c>
-      <c r="J16" s="6">
+      <c r="K16" s="3">
+        <v>1</v>
+      </c>
+      <c r="L16" s="32">
+        <v>7657</v>
+      </c>
+      <c r="M16" s="2">
         <v>0.90909090909090895</v>
       </c>
-      <c r="K16" s="7">
-        <v>1</v>
-      </c>
-      <c r="L16" s="8">
+      <c r="N16" s="34">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3">
         <v>0.75</v>
       </c>
-      <c r="M16" s="6">
-        <v>1</v>
-      </c>
-      <c r="N16" s="7">
-        <v>1</v>
-      </c>
-      <c r="O16" s="27">
-        <v>1</v>
+      <c r="P16" s="31">
+        <v>19745</v>
+      </c>
+      <c r="Q16" s="32">
+        <v>2</v>
+      </c>
+      <c r="R16" s="2">
+        <v>1</v>
+      </c>
+      <c r="S16" s="34">
+        <v>1</v>
+      </c>
+      <c r="T16" s="19">
+        <v>1</v>
+      </c>
+      <c r="U16" s="32">
+        <v>9236</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="9">
-        <v>1</v>
-      </c>
-      <c r="E17" s="10">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11">
-        <v>1</v>
-      </c>
-      <c r="G17" s="9">
-        <v>1</v>
-      </c>
-      <c r="H17" s="10">
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5">
+        <v>1</v>
+      </c>
+      <c r="G17" s="20">
+        <v>14865</v>
+      </c>
+      <c r="H17" s="42">
+        <v>1</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+      <c r="J17" s="5">
         <v>0.95454545454545403</v>
       </c>
-      <c r="I17" s="11">
-        <v>1</v>
-      </c>
-      <c r="J17" s="9">
+      <c r="K17" s="6">
+        <v>1</v>
+      </c>
+      <c r="L17" s="42">
+        <v>10115</v>
+      </c>
+      <c r="M17" s="4">
         <v>0.94117647058823495</v>
       </c>
-      <c r="K17" s="10">
+      <c r="N17" s="5">
         <v>0.952380952380952</v>
       </c>
-      <c r="L17" s="11">
-        <v>1</v>
-      </c>
-      <c r="M17" s="9">
-        <v>1</v>
-      </c>
-      <c r="N17" s="10">
-        <v>1</v>
-      </c>
-      <c r="O17" s="30">
-        <v>1</v>
+      <c r="O17" s="6">
+        <v>1</v>
+      </c>
+      <c r="P17" s="21">
+        <v>12597</v>
+      </c>
+      <c r="Q17" s="42">
+        <v>1</v>
+      </c>
+      <c r="R17" s="4">
+        <v>1</v>
+      </c>
+      <c r="S17" s="5">
+        <v>1</v>
+      </c>
+      <c r="T17" s="22">
+        <v>1</v>
+      </c>
+      <c r="U17" s="42">
+        <v>9107</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="19" t="s">
+      <c r="B18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="22">
-        <v>1</v>
-      </c>
-      <c r="E18" s="23">
-        <v>1</v>
-      </c>
-      <c r="F18" s="24">
-        <v>1</v>
-      </c>
-      <c r="G18" s="22">
-        <v>1</v>
-      </c>
-      <c r="H18" s="23">
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15">
+        <v>1</v>
+      </c>
+      <c r="G18" s="13">
+        <v>12275</v>
+      </c>
+      <c r="H18" s="12">
+        <v>1</v>
+      </c>
+      <c r="I18" s="14">
+        <v>1</v>
+      </c>
+      <c r="J18" s="15">
         <v>0.90909090909090895</v>
       </c>
-      <c r="I18" s="24">
-        <v>1</v>
-      </c>
-      <c r="J18" s="22">
-        <v>1</v>
-      </c>
-      <c r="K18" s="23">
+      <c r="K18" s="16">
+        <v>1</v>
+      </c>
+      <c r="L18" s="12">
+        <v>8925</v>
+      </c>
+      <c r="M18" s="14">
+        <v>1</v>
+      </c>
+      <c r="N18" s="15">
         <v>0.92307692307692302</v>
       </c>
-      <c r="L18" s="24">
-        <v>1</v>
-      </c>
-      <c r="M18" s="22">
-        <v>1</v>
-      </c>
-      <c r="N18" s="23">
-        <v>1</v>
-      </c>
-      <c r="O18" s="25">
-        <v>1</v>
+      <c r="O18" s="16">
+        <v>1</v>
+      </c>
+      <c r="P18" s="11">
+        <v>12593</v>
+      </c>
+      <c r="Q18" s="12">
+        <v>1</v>
+      </c>
+      <c r="R18" s="14">
+        <v>1</v>
+      </c>
+      <c r="S18" s="15">
+        <v>1</v>
+      </c>
+      <c r="T18" s="17">
+        <v>1</v>
+      </c>
+      <c r="U18" s="12">
+        <v>11146</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="26" t="s">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="2">
         <v>0.9375</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="34">
         <v>0.94117647058823495</v>
       </c>
-      <c r="F19" s="8">
-        <v>1</v>
-      </c>
-      <c r="G19" s="6">
-        <v>1</v>
-      </c>
-      <c r="H19" s="7">
+      <c r="F19" s="34">
+        <v>1</v>
+      </c>
+      <c r="G19" s="18">
+        <v>19259</v>
+      </c>
+      <c r="H19" s="32">
+        <v>2</v>
+      </c>
+      <c r="I19" s="2">
+        <v>1</v>
+      </c>
+      <c r="J19" s="34">
         <v>0.64285714285714202</v>
       </c>
-      <c r="I19" s="8">
-        <v>1</v>
-      </c>
-      <c r="J19" s="6">
+      <c r="K19" s="3">
+        <v>1</v>
+      </c>
+      <c r="L19" s="32">
+        <v>7462</v>
+      </c>
+      <c r="M19" s="2">
         <v>0.8</v>
       </c>
-      <c r="K19" s="7">
-        <v>1</v>
-      </c>
-      <c r="L19" s="8">
-        <v>1</v>
-      </c>
-      <c r="M19" s="6">
-        <v>1</v>
-      </c>
-      <c r="N19" s="7">
-        <v>1</v>
-      </c>
-      <c r="O19" s="27">
-        <v>1</v>
+      <c r="N19" s="34">
+        <v>1</v>
+      </c>
+      <c r="O19" s="3">
+        <v>1</v>
+      </c>
+      <c r="P19" s="31">
+        <v>13229</v>
+      </c>
+      <c r="Q19" s="32">
+        <v>1</v>
+      </c>
+      <c r="R19" s="2">
+        <v>1</v>
+      </c>
+      <c r="S19" s="34">
+        <v>1</v>
+      </c>
+      <c r="T19" s="19">
+        <v>1</v>
+      </c>
+      <c r="U19" s="32">
+        <v>7916</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="26" t="s">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="2">
         <v>0.91666666666666596</v>
       </c>
-      <c r="E20" s="7">
-        <v>1</v>
-      </c>
-      <c r="F20" s="8">
+      <c r="E20" s="34">
+        <v>1</v>
+      </c>
+      <c r="F20" s="34">
         <v>0.75</v>
       </c>
-      <c r="G20" s="6">
-        <v>1</v>
-      </c>
-      <c r="H20" s="7">
-        <v>1</v>
-      </c>
-      <c r="I20" s="8">
+      <c r="G20" s="18">
+        <v>13615</v>
+      </c>
+      <c r="H20" s="32">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2">
+        <v>1</v>
+      </c>
+      <c r="J20" s="34">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="J20" s="6">
-        <v>1</v>
-      </c>
-      <c r="K20" s="7">
-        <v>1</v>
-      </c>
-      <c r="L20" s="8">
+      <c r="L20" s="32">
+        <v>8820</v>
+      </c>
+      <c r="M20" s="2">
+        <v>1</v>
+      </c>
+      <c r="N20" s="34">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="M20" s="6">
-        <v>1</v>
-      </c>
-      <c r="N20" s="7">
-        <v>1</v>
-      </c>
-      <c r="O20" s="27">
-        <v>1</v>
+      <c r="P20" s="31">
+        <v>13562</v>
+      </c>
+      <c r="Q20" s="32">
+        <v>1</v>
+      </c>
+      <c r="R20" s="2">
+        <v>1</v>
+      </c>
+      <c r="S20" s="34">
+        <v>1</v>
+      </c>
+      <c r="T20" s="19">
+        <v>1</v>
+      </c>
+      <c r="U20" s="32">
+        <v>9736</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="2">
         <v>0.94444444444444398</v>
       </c>
-      <c r="E21" s="7">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8">
-        <v>1</v>
-      </c>
-      <c r="G21" s="6">
-        <v>1</v>
-      </c>
-      <c r="H21" s="7">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8">
-        <v>1</v>
-      </c>
-      <c r="J21" s="6">
-        <v>1</v>
-      </c>
-      <c r="K21" s="7">
-        <v>1</v>
-      </c>
-      <c r="L21" s="8">
-        <v>1</v>
-      </c>
-      <c r="M21" s="6">
+      <c r="E21" s="34">
+        <v>1</v>
+      </c>
+      <c r="F21" s="34">
+        <v>1</v>
+      </c>
+      <c r="G21" s="18">
+        <v>13440</v>
+      </c>
+      <c r="H21" s="32">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1</v>
+      </c>
+      <c r="J21" s="34">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
+      </c>
+      <c r="L21" s="32">
+        <v>10773</v>
+      </c>
+      <c r="M21" s="2">
+        <v>1</v>
+      </c>
+      <c r="N21" s="34">
+        <v>1</v>
+      </c>
+      <c r="O21" s="3">
+        <v>1</v>
+      </c>
+      <c r="P21" s="31">
+        <v>13796</v>
+      </c>
+      <c r="Q21" s="32">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2">
         <v>0.90909090909090895</v>
       </c>
-      <c r="N21" s="7">
-        <v>1</v>
-      </c>
-      <c r="O21" s="27">
-        <v>1</v>
+      <c r="S21" s="34">
+        <v>1</v>
+      </c>
+      <c r="T21" s="19">
+        <v>1</v>
+      </c>
+      <c r="U21" s="32">
+        <v>11661</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="28" t="s">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="9">
-        <v>1</v>
-      </c>
-      <c r="E22" s="10">
-        <v>1</v>
-      </c>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
-      <c r="G22" s="9">
-        <v>1</v>
-      </c>
-      <c r="H22" s="10">
-        <v>1</v>
-      </c>
-      <c r="I22" s="11">
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="G22" s="20">
+        <v>18272</v>
+      </c>
+      <c r="H22" s="42">
+        <v>1</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="6">
         <v>0.8</v>
       </c>
-      <c r="J22" s="9">
-        <v>1</v>
-      </c>
-      <c r="K22" s="10">
-        <v>1</v>
-      </c>
-      <c r="L22" s="11">
-        <v>1</v>
-      </c>
-      <c r="M22" s="9">
+      <c r="L22" s="42">
+        <v>11688</v>
+      </c>
+      <c r="M22" s="4">
+        <v>1</v>
+      </c>
+      <c r="N22" s="5">
+        <v>1</v>
+      </c>
+      <c r="O22" s="6">
+        <v>1</v>
+      </c>
+      <c r="P22" s="21">
+        <v>15634</v>
+      </c>
+      <c r="Q22" s="42">
+        <v>1</v>
+      </c>
+      <c r="R22" s="4">
         <v>0.93333333333333302</v>
       </c>
-      <c r="N22" s="10">
-        <v>1</v>
-      </c>
-      <c r="O22" s="30">
-        <v>1</v>
+      <c r="S22" s="5">
+        <v>1</v>
+      </c>
+      <c r="T22" s="22">
+        <v>1</v>
+      </c>
+      <c r="U22" s="42">
+        <v>13004</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A23" s="21" t="s">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D23" s="22">
-        <v>1</v>
-      </c>
-      <c r="E23" s="23">
-        <v>1</v>
-      </c>
-      <c r="F23" s="24">
-        <v>1</v>
-      </c>
-      <c r="G23" s="22">
-        <v>1</v>
-      </c>
-      <c r="H23" s="23">
-        <v>1</v>
-      </c>
-      <c r="I23" s="24">
-        <v>1</v>
-      </c>
-      <c r="J23" s="22">
-        <v>1</v>
-      </c>
-      <c r="K23" s="23">
-        <v>1</v>
-      </c>
-      <c r="L23" s="24">
-        <v>1</v>
-      </c>
-      <c r="M23" s="22">
-        <v>1</v>
-      </c>
-      <c r="N23" s="23">
-        <v>1</v>
-      </c>
-      <c r="O23" s="25">
-        <v>1</v>
+      <c r="D23" s="14">
+        <v>1</v>
+      </c>
+      <c r="E23" s="15">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
+      </c>
+      <c r="G23" s="18">
+        <v>24554</v>
+      </c>
+      <c r="H23" s="32">
+        <v>2</v>
+      </c>
+      <c r="I23" s="14">
+        <v>1</v>
+      </c>
+      <c r="J23" s="15">
+        <v>1</v>
+      </c>
+      <c r="K23" s="16">
+        <v>1</v>
+      </c>
+      <c r="L23" s="32">
+        <v>11381</v>
+      </c>
+      <c r="M23" s="14">
+        <v>1</v>
+      </c>
+      <c r="N23" s="15">
+        <v>1</v>
+      </c>
+      <c r="O23" s="16">
+        <v>1</v>
+      </c>
+      <c r="P23" s="31">
+        <v>17382</v>
+      </c>
+      <c r="Q23" s="32">
+        <v>1</v>
+      </c>
+      <c r="R23" s="14">
+        <v>1</v>
+      </c>
+      <c r="S23" s="15">
+        <v>1</v>
+      </c>
+      <c r="T23" s="17">
+        <v>1</v>
+      </c>
+      <c r="U23" s="32">
+        <v>12326</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="26" t="s">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="2">
         <v>0.86666666666666603</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="34">
         <v>0.95</v>
       </c>
-      <c r="F24" s="8">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8">
-        <v>1</v>
-      </c>
-      <c r="J24" s="6">
-        <v>1</v>
-      </c>
-      <c r="K24" s="7">
-        <v>1</v>
-      </c>
-      <c r="L24" s="8">
-        <v>1</v>
-      </c>
-      <c r="M24" s="6">
-        <v>1</v>
-      </c>
-      <c r="N24" s="7">
+      <c r="F24" s="34">
+        <v>1</v>
+      </c>
+      <c r="G24" s="18">
+        <v>15578</v>
+      </c>
+      <c r="H24" s="32">
+        <v>1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="34">
+        <v>1</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" s="32">
+        <v>11651</v>
+      </c>
+      <c r="M24" s="2">
+        <v>1</v>
+      </c>
+      <c r="N24" s="34">
+        <v>1</v>
+      </c>
+      <c r="O24" s="3">
+        <v>1</v>
+      </c>
+      <c r="P24" s="31">
+        <v>18017</v>
+      </c>
+      <c r="Q24" s="32">
+        <v>1</v>
+      </c>
+      <c r="R24" s="2">
+        <v>1</v>
+      </c>
+      <c r="S24" s="34">
         <v>0.95454545454545403</v>
       </c>
-      <c r="O24" s="27">
-        <v>1</v>
+      <c r="T24" s="19">
+        <v>1</v>
+      </c>
+      <c r="U24" s="32">
+        <v>11941</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="26" t="s">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" t="s">
         <v>43</v>
       </c>
-      <c r="D25" s="6">
-        <v>1</v>
-      </c>
-      <c r="E25" s="7">
+      <c r="D25" s="2">
+        <v>1</v>
+      </c>
+      <c r="E25" s="34">
         <v>0.94736842105263097</v>
       </c>
-      <c r="F25" s="8">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6">
-        <v>1</v>
-      </c>
-      <c r="H25" s="7">
-        <v>1</v>
-      </c>
-      <c r="I25" s="8">
-        <v>1</v>
-      </c>
-      <c r="J25" s="6">
-        <v>1</v>
-      </c>
-      <c r="K25" s="7">
-        <v>1</v>
-      </c>
-      <c r="L25" s="8">
-        <v>1</v>
-      </c>
-      <c r="M25" s="6">
-        <v>1</v>
-      </c>
-      <c r="N25" s="7">
-        <v>1</v>
-      </c>
-      <c r="O25" s="27">
-        <v>1</v>
+      <c r="F25" s="34">
+        <v>1</v>
+      </c>
+      <c r="G25" s="18">
+        <v>18393</v>
+      </c>
+      <c r="H25" s="32">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="34">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1</v>
+      </c>
+      <c r="L25" s="32">
+        <v>11710</v>
+      </c>
+      <c r="M25" s="2">
+        <v>1</v>
+      </c>
+      <c r="N25" s="34">
+        <v>1</v>
+      </c>
+      <c r="O25" s="3">
+        <v>1</v>
+      </c>
+      <c r="P25" s="31">
+        <v>30484</v>
+      </c>
+      <c r="Q25" s="32">
+        <v>2</v>
+      </c>
+      <c r="R25" s="2">
+        <v>1</v>
+      </c>
+      <c r="S25" s="34">
+        <v>1</v>
+      </c>
+      <c r="T25" s="19">
+        <v>1</v>
+      </c>
+      <c r="U25" s="32">
+        <v>11743</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A26" s="26" t="s">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" t="s">
         <v>18</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" t="s">
         <v>44</v>
       </c>
-      <c r="D26" s="6">
-        <v>1</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1</v>
-      </c>
-      <c r="F26" s="8">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7">
-        <v>1</v>
-      </c>
-      <c r="I26" s="8">
-        <v>1</v>
-      </c>
-      <c r="J26" s="6">
-        <v>1</v>
-      </c>
-      <c r="K26" s="7">
-        <v>1</v>
-      </c>
-      <c r="L26" s="8">
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="34">
+        <v>1</v>
+      </c>
+      <c r="F26" s="34">
+        <v>1</v>
+      </c>
+      <c r="G26" s="18">
+        <v>18983</v>
+      </c>
+      <c r="H26" s="32">
+        <v>1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="34">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3">
+        <v>1</v>
+      </c>
+      <c r="L26" s="32">
+        <v>10891</v>
+      </c>
+      <c r="M26" s="2">
+        <v>1</v>
+      </c>
+      <c r="N26" s="34">
+        <v>1</v>
+      </c>
+      <c r="O26" s="3">
         <v>0.85714285714285698</v>
       </c>
-      <c r="M26" s="6">
-        <v>1</v>
-      </c>
-      <c r="N26" s="7">
-        <v>1</v>
-      </c>
-      <c r="O26" s="27">
-        <v>1</v>
+      <c r="P26" s="31">
+        <v>20151</v>
+      </c>
+      <c r="Q26" s="32">
+        <v>1</v>
+      </c>
+      <c r="R26" s="2">
+        <v>1</v>
+      </c>
+      <c r="S26" s="34">
+        <v>1</v>
+      </c>
+      <c r="T26" s="19">
+        <v>1</v>
+      </c>
+      <c r="U26" s="32">
+        <v>13002</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="28" t="s">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="4">
         <v>0.86666666666666603</v>
       </c>
-      <c r="E27" s="10">
-        <v>1</v>
-      </c>
-      <c r="F27" s="11">
-        <v>1</v>
-      </c>
-      <c r="G27" s="9">
-        <v>1</v>
-      </c>
-      <c r="H27" s="10">
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5">
+        <v>1</v>
+      </c>
+      <c r="G27" s="18">
+        <v>17457</v>
+      </c>
+      <c r="H27" s="32">
+        <v>1</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+      <c r="J27" s="5">
         <v>0.952380952380952</v>
       </c>
-      <c r="I27" s="11">
-        <v>1</v>
-      </c>
-      <c r="J27" s="9">
-        <v>1</v>
-      </c>
-      <c r="K27" s="10">
-        <v>1</v>
-      </c>
-      <c r="L27" s="11">
-        <v>1</v>
-      </c>
-      <c r="M27" s="9">
-        <v>1</v>
-      </c>
-      <c r="N27" s="10">
+      <c r="K27" s="6">
+        <v>1</v>
+      </c>
+      <c r="L27" s="32">
+        <v>12779</v>
+      </c>
+      <c r="M27" s="4">
+        <v>1</v>
+      </c>
+      <c r="N27" s="5">
+        <v>1</v>
+      </c>
+      <c r="O27" s="6">
+        <v>1</v>
+      </c>
+      <c r="P27" s="31">
+        <v>17201</v>
+      </c>
+      <c r="Q27" s="32">
+        <v>1</v>
+      </c>
+      <c r="R27" s="4">
+        <v>1</v>
+      </c>
+      <c r="S27" s="5">
         <v>0.90909090909090895</v>
       </c>
-      <c r="O27" s="30">
-        <v>1</v>
+      <c r="T27" s="22">
+        <v>1</v>
+      </c>
+      <c r="U27" s="32">
+        <v>12517</v>
       </c>
     </row>
-    <row r="28" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C28" s="21" t="s">
+    <row r="28" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C28" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="7">
         <f>AVERAGE(D3:D27)</f>
         <v>0.97204700854700843</v>
       </c>
-      <c r="E28" s="13">
-        <f t="shared" ref="E28:O28" si="0">AVERAGE(E3:E27)</f>
+      <c r="E28" s="8">
+        <f t="shared" ref="E28:G28" si="0">AVERAGE(E3:E27)</f>
         <v>0.98721431028551765</v>
       </c>
-      <c r="F28" s="14">
-        <f t="shared" si="0"/>
+      <c r="F28" s="8">
+        <f>AVERAGE(F3:F27)</f>
         <v>0.96666666666666656</v>
       </c>
-      <c r="G28" s="12">
-        <f t="shared" si="0"/>
+      <c r="G28" s="41">
+        <f>AVERAGE(G3:G27)</f>
+        <v>16870.72</v>
+      </c>
+      <c r="H28" s="33">
+        <f>COUNTIF(H3:H27,2)</f>
+        <v>6</v>
+      </c>
+      <c r="I28" s="7">
+        <f>AVERAGE(I3:I27)</f>
         <v>0.98533333333333328</v>
       </c>
-      <c r="H28" s="13">
-        <f t="shared" si="0"/>
+      <c r="J28" s="8">
+        <f>AVERAGE(J3:J27)</f>
         <v>0.96231846229928053</v>
       </c>
-      <c r="I28" s="14">
-        <f t="shared" si="0"/>
+      <c r="K28" s="9">
+        <f>AVERAGE(K3:K27)</f>
         <v>0.90866666666666662</v>
       </c>
-      <c r="J28" s="12">
-        <f t="shared" si="0"/>
+      <c r="L28" s="41">
+        <f>AVERAGE(L3:L27)</f>
+        <v>10250.719999999999</v>
+      </c>
+      <c r="M28" s="7">
+        <f>AVERAGE(M3:M27)</f>
         <v>0.98601069518716566</v>
       </c>
-      <c r="K28" s="13">
-        <f t="shared" si="0"/>
+      <c r="N28" s="8">
+        <f>AVERAGE(N3:N27)</f>
         <v>0.98141251791686568</v>
       </c>
-      <c r="L28" s="14">
-        <f t="shared" si="0"/>
+      <c r="O28" s="9">
+        <f>AVERAGE(O3:O27)</f>
         <v>0.88470995670995667</v>
       </c>
-      <c r="M28" s="12">
-        <f t="shared" si="0"/>
+      <c r="P28" s="41">
+        <f>AVERAGE(P3:P27)</f>
+        <v>16484.48</v>
+      </c>
+      <c r="Q28" s="33">
+        <f>COUNTIF(Q3:Q27,2)</f>
+        <v>3</v>
+      </c>
+      <c r="R28" s="7">
+        <f>AVERAGE(R3:R27)</f>
         <v>0.99103030303030304</v>
       </c>
-      <c r="N28" s="13">
-        <f t="shared" si="0"/>
+      <c r="S28" s="8">
+        <f>AVERAGE(S3:S27)</f>
         <v>0.98063519813519806</v>
       </c>
-      <c r="O28" s="14">
-        <f t="shared" si="0"/>
+      <c r="T28" s="9">
+        <f>AVERAGE(T3:T27)</f>
         <v>0.97333333333333327</v>
       </c>
+      <c r="U28" s="41">
+        <f>AVERAGE(U3:U27)</f>
+        <v>10966.28</v>
+      </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C29" s="26" t="s">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C29" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="36">
         <f>25-COUNTIF(D3:D27,1)</f>
         <v>6</v>
       </c>
-      <c r="E29" s="16">
+      <c r="E29" s="37">
         <f t="shared" ref="E29:F29" si="1">25-COUNTIF(E3:E27,1)</f>
         <v>6</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="38">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="G29" s="15">
-        <f>25-COUNTIF(G3:G27,1)</f>
+      <c r="I29" s="36">
+        <f>25-COUNTIF(I3:I27,1)</f>
         <v>3</v>
       </c>
-      <c r="H29" s="16">
-        <f t="shared" ref="H29:I29" si="2">25-COUNTIF(H3:H27,1)</f>
+      <c r="J29" s="37">
+        <f t="shared" ref="J29:K29" si="2">25-COUNTIF(J3:J27,1)</f>
         <v>8</v>
       </c>
-      <c r="I29" s="17">
+      <c r="K29" s="38">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="J29" s="15">
-        <f>25-COUNTIF(J3:J27,1)</f>
+      <c r="M29" s="36">
+        <f>25-COUNTIF(M3:M27,1)</f>
         <v>3</v>
       </c>
-      <c r="K29" s="16">
-        <f t="shared" ref="K29:L29" si="3">25-COUNTIF(K3:K27,1)</f>
+      <c r="N29" s="37">
+        <f t="shared" ref="N29:O29" si="3">25-COUNTIF(N3:N27,1)</f>
         <v>6</v>
       </c>
-      <c r="L29" s="17">
+      <c r="O29" s="38">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="M29" s="15">
-        <f>25-COUNTIF(M3:M27,1)</f>
+      <c r="R29" s="36">
+        <f>25-COUNTIF(R3:R27,1)</f>
         <v>3</v>
       </c>
-      <c r="N29" s="16">
-        <f t="shared" ref="N29:O29" si="4">25-COUNTIF(N3:N27,1)</f>
+      <c r="S29" s="37">
+        <f t="shared" ref="S29:T29" si="4">25-COUNTIF(S3:S27,1)</f>
         <v>6</v>
       </c>
-      <c r="O29" s="17">
+      <c r="T29" s="38">
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="C30" s="28" t="s">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="C30" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="28">
         <f>AVERAGE(D29:F29)</f>
         <v>5</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="31">
-        <f>AVERAGE(G29:I29)</f>
+      <c r="E30" s="29"/>
+      <c r="F30" s="30"/>
+      <c r="I30" s="28">
+        <f>AVERAGE(I29:K29)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="H30" s="32"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="31">
-        <f>AVERAGE(J29:L29)</f>
+      <c r="J30" s="29"/>
+      <c r="K30" s="30"/>
+      <c r="M30" s="28">
+        <f>AVERAGE(M29:O29)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="K30" s="32"/>
-      <c r="L30" s="33"/>
-      <c r="M30" s="31">
-        <f>AVERAGE(M29:O29)</f>
+      <c r="N30" s="29"/>
+      <c r="O30" s="30"/>
+      <c r="R30" s="28">
+        <f>AVERAGE(R29:T29)</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="N30" s="32"/>
-      <c r="O30" s="33"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="30"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="G31">
+        <f>SUM(G3:G27)</f>
+        <v>421768</v>
+      </c>
+      <c r="L31">
+        <f>SUM(L3:L27)</f>
+        <v>256268</v>
+      </c>
+      <c r="P31">
+        <f>SUM(P3:P27)</f>
+        <v>412112</v>
+      </c>
+      <c r="U31">
+        <f>SUM(U3:U27)</f>
+        <v>274157</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:I1"/>
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="M1:O1"/>
+    <mergeCell ref="M30:O30"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="D1:H1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:U1"/>
     <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="M30:O30"/>
   </mergeCells>
-  <conditionalFormatting sqref="D3:O28">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="R3:T28 I3:K28 D3:F28 M3:O28">
+    <cfRule type="colorScale" priority="32">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7878,8 +9308,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D28:O28">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="R28:T28 I28:K28 D28:F28 M28:O28">
+    <cfRule type="colorScale" priority="37">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -7890,8 +9320,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D29:O29">
-    <cfRule type="dataBar" priority="1">
+  <conditionalFormatting sqref="R29:T29 I29:K29 D29:F29 M29:O29">
+    <cfRule type="dataBar" priority="42">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -7904,7 +9334,82 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G27 L3:L27 P3:P27 U3:U27">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H27 Q3:Q27">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L28 G28 P28 U28">
+    <cfRule type="dataBar" priority="5">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8DBD9729-F9A2-4FD1-B0AB-CF3111D1A845}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G27">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L27">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:P27">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U3:U27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -7919,7 +9424,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D29:O29</xm:sqref>
+          <xm:sqref>R29:T29 I29:K29 D29:F29 M29:O29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8DBD9729-F9A2-4FD1-B0AB-CF3111D1A845}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L28 G28 P28 U28</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/test/results/model_comparison/comparison.xlsx
+++ b/test/results/model_comparison/comparison.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Levi\PyCharmProjects\jogi-agent-rag\test\results\model_comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FCDF3A6-DB83-47DD-A0F3-E8B5CD9E8339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9123FCFB-51BA-402D-9336-B54E6A7E4679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D9DAACF3-2B6D-4249-925C-DCD65B142A30}"/>
   </bookViews>
   <sheets>
     <sheet name="Összefoglaló" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="58">
   <si>
     <t>Base Model</t>
   </si>
@@ -49,9 +49,6 @@
   </si>
   <si>
     <t>Unified Model (Researcher+Grounding Verifier)</t>
-  </si>
-  <si>
-    <t>Unified Model without Verifier</t>
   </si>
   <si>
     <t>Faithfulness</t>
@@ -202,6 +199,21 @@
   </si>
   <si>
     <t>Verifier Runs</t>
+  </si>
+  <si>
+    <t>Unified Model (1-3) without Verifier</t>
+  </si>
+  <si>
+    <t>Unified Model 1-3 without Verifier</t>
+  </si>
+  <si>
+    <t>Unified Model 2-4 without Verifier</t>
+  </si>
+  <si>
+    <t>Unified Model (2-3) without Verifier</t>
+  </si>
+  <si>
+    <t>Unified Model (2-4) without Verifier</t>
   </si>
 </sst>
 </file>
@@ -547,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -573,6 +585,25 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -582,27 +613,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -710,7 +720,7 @@
                   <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Unified Model without Verifier</c:v>
+                  <c:v>Unified Model (2-3) without Verifier</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1010,7 +1020,7 @@
                   <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Unified Model without Verifier</c:v>
+                  <c:v>Unified Model (2-3) without Verifier</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1310,7 +1320,7 @@
                   <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Unified Model without Verifier</c:v>
+                  <c:v>Unified Model (2-3) without Verifier</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1618,7 +1628,7 @@
                   <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Unified Model without Verifier</c:v>
+                  <c:v>Unified Model (2-3) without Verifier</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1933,7 +1943,7 @@
                   <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Unified Model without Verifier</c:v>
+                  <c:v>Unified Model (2-3) without Verifier</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2244,7 +2254,7 @@
                   <c:v>Unified Model (Researcher+Grounding Verifier)</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>Unified Model without Verifier</c:v>
+                  <c:v>Unified Model (2-3) without Verifier</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7132,16 +7142,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA46300E-0F1F-4949-90ED-4C2BDEB1CA35}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="27.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -7152,12 +7163,18 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>4</v>
       </c>
       <c r="B2">
         <v>0.97204699999999999</v>
@@ -7171,10 +7188,16 @@
       <c r="E2">
         <v>0.99102999999999997</v>
       </c>
+      <c r="F2">
+        <v>0.98959200000000003</v>
+      </c>
+      <c r="G2">
+        <v>0.98220799999999997</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
         <v>2.8000000000000001E-2</v>
@@ -7188,10 +7211,16 @@
       <c r="E3" s="1">
         <v>8.9999999999999993E-3</v>
       </c>
+      <c r="F3" s="1">
+        <v>1.04E-2</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.78E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>0.98721400000000004</v>
@@ -7205,10 +7234,16 @@
       <c r="E4">
         <v>0.98063500000000003</v>
       </c>
+      <c r="F4">
+        <v>0.98738400000000004</v>
+      </c>
+      <c r="G4">
+        <v>0.96244200000000002</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0.96666700000000005</v>
@@ -7222,10 +7257,16 @@
       <c r="E5">
         <v>0.973333</v>
       </c>
+      <c r="F5">
+        <v>0.92</v>
+      </c>
+      <c r="G5">
+        <v>0.91266700000000001</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>16870.72</v>
@@ -7239,10 +7280,16 @@
       <c r="E6">
         <v>10966.28</v>
       </c>
+      <c r="F6">
+        <v>12224.56</v>
+      </c>
+      <c r="G6">
+        <v>12087.56</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7">
         <v>23.34</v>
@@ -7256,31 +7303,73 @@
       <c r="E7">
         <v>16.37</v>
       </c>
+      <c r="F7">
+        <v>19.13</v>
+      </c>
+      <c r="G7">
+        <v>16.32</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:E2">
+  <conditionalFormatting sqref="B2:G2">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:E3">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B4:G4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:G5 F6">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -7292,7 +7381,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B3:E3">
+  <conditionalFormatting sqref="B6:E6">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -7304,31 +7393,31 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B4:E4">
+  <conditionalFormatting sqref="B7:G7">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:E5">
+  <conditionalFormatting sqref="B8:E8">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B6:E6">
+  <conditionalFormatting sqref="B3:F3">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7340,7 +7429,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B7:E7">
+  <conditionalFormatting sqref="B6:G6">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7352,7 +7441,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:E8">
+  <conditionalFormatting sqref="B3:G3">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7371,7 +7460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36BC549-5F0D-4260-974E-C5029CF103D9}">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
@@ -7388,110 +7477,148 @@
     <col min="17" max="17" width="11.77734375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="16.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="D1" s="25" t="s">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="D1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="25" t="s">
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="40"/>
+      <c r="M1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="25" t="s">
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="40"/>
+      <c r="R1" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="S1" s="39"/>
+      <c r="T1" s="39"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="38" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" s="39"/>
+      <c r="X1" s="39"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA1" s="39"/>
+      <c r="AB1" s="39"/>
+      <c r="AC1" s="40"/>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="27"/>
+      <c r="E2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="H2" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="M2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="P2" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="R2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="S2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="T2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="U2" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="W2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="X2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y2" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC2" s="32" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="H2" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="J2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="N2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q2" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="R2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="S2" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="T2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="U2" s="40" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="14">
         <v>1</v>
@@ -7547,211 +7674,307 @@
       <c r="U3" s="12">
         <v>8785</v>
       </c>
+      <c r="V3" s="14">
+        <v>1</v>
+      </c>
+      <c r="W3" s="15">
+        <v>1</v>
+      </c>
+      <c r="X3" s="17">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="Y3" s="12">
+        <v>11313</v>
+      </c>
+      <c r="Z3" s="14">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="12">
+        <v>9207</v>
+      </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D4" s="2">
         <v>0.76923076923076905</v>
       </c>
-      <c r="E4" s="34">
-        <v>1</v>
-      </c>
-      <c r="F4" s="34">
+      <c r="E4" s="27">
+        <v>1</v>
+      </c>
+      <c r="F4" s="27">
         <v>0.75</v>
       </c>
       <c r="G4" s="18">
         <v>19524</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="25">
         <v>2</v>
       </c>
       <c r="I4" s="2">
         <v>0.91666666666666596</v>
       </c>
-      <c r="J4" s="34">
+      <c r="J4" s="27">
         <v>1</v>
       </c>
       <c r="K4" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="L4" s="32">
+      <c r="L4" s="25">
         <v>8567</v>
       </c>
       <c r="M4" s="2">
         <v>1</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="27">
         <v>1</v>
       </c>
       <c r="O4" s="3">
         <v>0.5</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4">
         <v>12488</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="25">
         <v>1</v>
       </c>
       <c r="R4" s="2">
         <v>1</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="27">
         <v>0.92307692307692302</v>
       </c>
       <c r="T4" s="19">
         <v>1</v>
       </c>
-      <c r="U4" s="32">
+      <c r="U4" s="25">
         <v>9699</v>
       </c>
+      <c r="V4" s="2">
+        <v>0.9375</v>
+      </c>
+      <c r="W4" s="27">
+        <v>1</v>
+      </c>
+      <c r="X4" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="25">
+        <v>10429</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="19">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="AC4" s="25">
+        <v>9751</v>
+      </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A5" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="34">
-        <v>1</v>
-      </c>
-      <c r="F5" s="34">
+      <c r="E5" s="27">
+        <v>1</v>
+      </c>
+      <c r="F5" s="27">
         <v>0.66666666666666596</v>
       </c>
       <c r="G5" s="18">
         <v>12292</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="25">
         <v>1</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J5" s="27">
         <v>0.8125</v>
       </c>
       <c r="K5" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="L5" s="32">
+      <c r="L5" s="25">
         <v>8882</v>
       </c>
       <c r="M5" s="2">
         <v>1</v>
       </c>
-      <c r="N5" s="34">
+      <c r="N5" s="27">
         <v>0.95652173913043403</v>
       </c>
       <c r="O5" s="3">
         <v>0.6</v>
       </c>
-      <c r="P5" s="31">
+      <c r="P5">
         <v>15949</v>
       </c>
-      <c r="Q5" s="32">
+      <c r="Q5" s="25">
         <v>1</v>
       </c>
       <c r="R5" s="2">
         <v>0.93333333333333302</v>
       </c>
-      <c r="S5" s="34">
+      <c r="S5" s="27">
         <v>1</v>
       </c>
       <c r="T5" s="19">
         <v>1</v>
       </c>
-      <c r="U5" s="32">
+      <c r="U5" s="25">
         <v>8315</v>
       </c>
+      <c r="V5" s="2">
+        <v>1</v>
+      </c>
+      <c r="W5" s="27">
+        <v>1</v>
+      </c>
+      <c r="X5" s="19">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="Y5" s="25">
+        <v>9257</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="27">
+        <v>0.78571428571428503</v>
+      </c>
+      <c r="AB5" s="19">
+        <v>0.75</v>
+      </c>
+      <c r="AC5" s="25">
+        <v>11129</v>
+      </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
       <c r="D6" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="34">
+      <c r="E6" s="27">
         <v>0.94444444444444398</v>
       </c>
-      <c r="F6" s="34">
+      <c r="F6" s="27">
         <v>1</v>
       </c>
       <c r="G6" s="18">
         <v>13206</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="25">
         <v>1</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="34">
+      <c r="J6" s="27">
         <v>1</v>
       </c>
       <c r="K6" s="3">
         <v>1</v>
       </c>
-      <c r="L6" s="32">
+      <c r="L6" s="25">
         <v>10926</v>
       </c>
       <c r="M6" s="2">
         <v>1</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="27">
         <v>1</v>
       </c>
       <c r="O6" s="3">
         <v>0.8</v>
       </c>
-      <c r="P6" s="31">
+      <c r="P6">
         <v>15433</v>
       </c>
-      <c r="Q6" s="32">
+      <c r="Q6" s="25">
         <v>1</v>
       </c>
       <c r="R6" s="2">
         <v>1</v>
       </c>
-      <c r="S6" s="34">
+      <c r="S6" s="27">
         <v>1</v>
       </c>
       <c r="T6" s="19">
         <v>1</v>
       </c>
-      <c r="U6" s="32">
+      <c r="U6" s="25">
         <v>11617</v>
       </c>
+      <c r="V6" s="2">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="W6" s="27">
+        <v>1</v>
+      </c>
+      <c r="X6" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="25">
+        <v>13670</v>
+      </c>
+      <c r="Z6" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="25">
+        <v>11945</v>
+      </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A7" s="20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D7" s="4">
         <v>1</v>
@@ -7765,7 +7988,7 @@
       <c r="G7" s="20">
         <v>13709</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="34">
         <v>1</v>
       </c>
       <c r="I7" s="4">
@@ -7777,7 +8000,7 @@
       <c r="K7" s="6">
         <v>1</v>
       </c>
-      <c r="L7" s="42">
+      <c r="L7" s="34">
         <v>10360</v>
       </c>
       <c r="M7" s="4">
@@ -7792,7 +8015,7 @@
       <c r="P7" s="21">
         <v>21275</v>
       </c>
-      <c r="Q7" s="42">
+      <c r="Q7" s="34">
         <v>2</v>
       </c>
       <c r="R7" s="4">
@@ -7804,19 +8027,43 @@
       <c r="T7" s="22">
         <v>1</v>
       </c>
-      <c r="U7" s="42">
+      <c r="U7" s="34">
         <v>9958</v>
       </c>
+      <c r="V7" s="4">
+        <v>1</v>
+      </c>
+      <c r="W7" s="5">
+        <v>1</v>
+      </c>
+      <c r="X7" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="34">
+        <v>11953</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="34">
+        <v>12097</v>
+      </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" s="14">
         <v>1</v>
@@ -7872,211 +8119,307 @@
       <c r="U8" s="12">
         <v>9696</v>
       </c>
+      <c r="V8" s="14">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="W8" s="15">
+        <v>1</v>
+      </c>
+      <c r="X8" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="12">
+        <v>9603</v>
+      </c>
+      <c r="Z8" s="14">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="15">
+        <v>0.5625</v>
+      </c>
+      <c r="AB8" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="AC8" s="12">
+        <v>12994</v>
+      </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A9" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="2">
         <v>1</v>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="27">
         <v>0.95</v>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="27">
         <v>1</v>
       </c>
       <c r="G9" s="18">
         <v>17389</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="25">
         <v>1</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J9" s="27">
         <v>1</v>
       </c>
       <c r="K9" s="3">
         <v>1</v>
       </c>
-      <c r="L9" s="32">
+      <c r="L9" s="25">
         <v>14124</v>
       </c>
       <c r="M9" s="2">
         <v>1</v>
       </c>
-      <c r="N9" s="34">
+      <c r="N9" s="27">
         <v>0.83333333333333304</v>
       </c>
       <c r="O9" s="3">
         <v>1</v>
       </c>
-      <c r="P9" s="31">
+      <c r="P9">
         <v>19615</v>
       </c>
-      <c r="Q9" s="32">
+      <c r="Q9" s="25">
         <v>1</v>
       </c>
       <c r="R9" s="2">
         <v>1</v>
       </c>
-      <c r="S9" s="34">
+      <c r="S9" s="27">
         <v>0.95833333333333304</v>
       </c>
       <c r="T9" s="19">
         <v>1</v>
       </c>
-      <c r="U9" s="32">
+      <c r="U9" s="25">
         <v>11901</v>
       </c>
+      <c r="V9" s="2">
+        <v>1</v>
+      </c>
+      <c r="W9" s="27">
+        <v>0.96666666666666601</v>
+      </c>
+      <c r="X9" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="25">
+        <v>12685</v>
+      </c>
+      <c r="Z9" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="25">
+        <v>12933</v>
+      </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2">
         <v>1</v>
       </c>
-      <c r="E10" s="34">
-        <v>1</v>
-      </c>
-      <c r="F10" s="34">
+      <c r="E10" s="27">
+        <v>1</v>
+      </c>
+      <c r="F10" s="27">
         <v>1</v>
       </c>
       <c r="G10" s="18">
         <v>16060</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="25">
         <v>1</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
       </c>
-      <c r="J10" s="34">
+      <c r="J10" s="27">
         <v>1</v>
       </c>
       <c r="K10" s="3">
         <v>0.75</v>
       </c>
-      <c r="L10" s="32">
+      <c r="L10" s="25">
         <v>10520</v>
       </c>
       <c r="M10" s="2">
         <v>1</v>
       </c>
-      <c r="N10" s="34">
+      <c r="N10" s="27">
         <v>1</v>
       </c>
       <c r="O10" s="3">
         <v>1</v>
       </c>
-      <c r="P10" s="31">
+      <c r="P10">
         <v>15794</v>
       </c>
-      <c r="Q10" s="32">
+      <c r="Q10" s="25">
         <v>1</v>
       </c>
       <c r="R10" s="2">
         <v>1</v>
       </c>
-      <c r="S10" s="34">
+      <c r="S10" s="27">
         <v>1</v>
       </c>
       <c r="T10" s="19">
         <v>1</v>
       </c>
-      <c r="U10" s="32">
+      <c r="U10" s="25">
         <v>10610</v>
       </c>
+      <c r="V10" s="2">
+        <v>1</v>
+      </c>
+      <c r="W10" s="27">
+        <v>1</v>
+      </c>
+      <c r="X10" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="25">
+        <v>10768</v>
+      </c>
+      <c r="Z10" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="25">
+        <v>10080</v>
+      </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="34">
-        <v>1</v>
-      </c>
-      <c r="F11" s="34">
+      <c r="E11" s="27">
+        <v>1</v>
+      </c>
+      <c r="F11" s="27">
         <v>1</v>
       </c>
       <c r="G11" s="18">
         <v>17608</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="25">
         <v>1</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="27">
         <v>1</v>
       </c>
       <c r="K11" s="3">
         <v>1</v>
       </c>
-      <c r="L11" s="32">
+      <c r="L11" s="25">
         <v>11456</v>
       </c>
       <c r="M11" s="2">
         <v>1</v>
       </c>
-      <c r="N11" s="34">
+      <c r="N11" s="27">
         <v>1</v>
       </c>
       <c r="O11" s="3">
         <v>0.8</v>
       </c>
-      <c r="P11" s="31">
+      <c r="P11">
         <v>16891</v>
       </c>
-      <c r="Q11" s="32">
+      <c r="Q11" s="25">
         <v>1</v>
       </c>
       <c r="R11" s="2">
         <v>1</v>
       </c>
-      <c r="S11" s="34">
+      <c r="S11" s="27">
         <v>1</v>
       </c>
       <c r="T11" s="19">
         <v>1</v>
       </c>
-      <c r="U11" s="32">
+      <c r="U11" s="25">
         <v>16027</v>
       </c>
+      <c r="V11" s="2">
+        <v>1</v>
+      </c>
+      <c r="W11" s="27">
+        <v>1</v>
+      </c>
+      <c r="X11" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="25">
+        <v>13270</v>
+      </c>
+      <c r="Z11" s="2">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="AA11" s="27">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="AB11" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="25">
+        <v>12536</v>
+      </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4">
         <v>1</v>
@@ -8090,7 +8433,7 @@
       <c r="G12" s="20">
         <v>26389</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="34">
         <v>2</v>
       </c>
       <c r="I12" s="4">
@@ -8102,7 +8445,7 @@
       <c r="K12" s="6">
         <v>0.75</v>
       </c>
-      <c r="L12" s="42">
+      <c r="L12" s="34">
         <v>10454</v>
       </c>
       <c r="M12" s="4">
@@ -8117,7 +8460,7 @@
       <c r="P12" s="21">
         <v>15280</v>
       </c>
-      <c r="Q12" s="42">
+      <c r="Q12" s="34">
         <v>1</v>
       </c>
       <c r="R12" s="4">
@@ -8129,19 +8472,43 @@
       <c r="T12" s="22">
         <v>1</v>
       </c>
-      <c r="U12" s="42">
+      <c r="U12" s="34">
         <v>10015</v>
       </c>
+      <c r="V12" s="4">
+        <v>1</v>
+      </c>
+      <c r="W12" s="5">
+        <v>1</v>
+      </c>
+      <c r="X12" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="34">
+        <v>11557</v>
+      </c>
+      <c r="Z12" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="34">
+        <v>13320</v>
+      </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>31</v>
       </c>
       <c r="D13" s="14">
         <v>1</v>
@@ -8197,211 +8564,307 @@
       <c r="U13" s="12">
         <v>12082</v>
       </c>
+      <c r="V13" s="14">
+        <v>1</v>
+      </c>
+      <c r="W13" s="15">
+        <v>1</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>11105</v>
+      </c>
+      <c r="Z13" s="14">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0.4</v>
+      </c>
+      <c r="AC13" s="12">
+        <v>11541</v>
+      </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="E14" s="34">
-        <v>1</v>
-      </c>
-      <c r="F14" s="34">
+      <c r="E14" s="27">
+        <v>1</v>
+      </c>
+      <c r="F14" s="27">
         <v>1</v>
       </c>
       <c r="G14" s="18">
         <v>25681</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="25">
         <v>2</v>
       </c>
       <c r="I14" s="2">
         <v>1</v>
       </c>
-      <c r="J14" s="34">
+      <c r="J14" s="27">
         <v>1</v>
       </c>
       <c r="K14" s="3">
         <v>1</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="25">
         <v>9586</v>
       </c>
       <c r="M14" s="2">
         <v>1</v>
       </c>
-      <c r="N14" s="34">
+      <c r="N14" s="27">
         <v>1</v>
       </c>
       <c r="O14" s="3">
         <v>1</v>
       </c>
-      <c r="P14" s="31">
+      <c r="P14">
         <v>15989</v>
       </c>
-      <c r="Q14" s="32">
+      <c r="Q14" s="25">
         <v>1</v>
       </c>
       <c r="R14" s="2">
         <v>1</v>
       </c>
-      <c r="S14" s="34">
+      <c r="S14" s="27">
         <v>1</v>
       </c>
       <c r="T14" s="19">
         <v>1</v>
       </c>
-      <c r="U14" s="32">
+      <c r="U14" s="25">
         <v>10980</v>
       </c>
+      <c r="V14" s="2">
+        <v>1</v>
+      </c>
+      <c r="W14" s="27">
+        <v>1</v>
+      </c>
+      <c r="X14" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="25">
+        <v>12761</v>
+      </c>
+      <c r="Z14" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="27">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="AB14" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="25">
+        <v>10991</v>
+      </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A15" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" s="2">
         <v>1</v>
       </c>
-      <c r="E15" s="34">
-        <v>1</v>
-      </c>
-      <c r="F15" s="34">
+      <c r="E15" s="27">
+        <v>1</v>
+      </c>
+      <c r="F15" s="27">
         <v>1</v>
       </c>
       <c r="G15" s="18">
         <v>23739</v>
       </c>
-      <c r="H15" s="32">
+      <c r="H15" s="25">
         <v>2</v>
       </c>
       <c r="I15" s="2">
         <v>1</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="27">
         <v>1</v>
       </c>
       <c r="K15" s="3">
         <v>1</v>
       </c>
-      <c r="L15" s="32">
+      <c r="L15" s="25">
         <v>11563</v>
       </c>
       <c r="M15" s="2">
         <v>1</v>
       </c>
-      <c r="N15" s="34">
+      <c r="N15" s="27">
         <v>1</v>
       </c>
       <c r="O15" s="3">
         <v>0.72727272727272696</v>
       </c>
-      <c r="P15" s="31">
+      <c r="P15">
         <v>18430</v>
       </c>
-      <c r="Q15" s="32">
+      <c r="Q15" s="25">
         <v>1</v>
       </c>
       <c r="R15" s="2">
         <v>1</v>
       </c>
-      <c r="S15" s="34">
+      <c r="S15" s="27">
         <v>1</v>
       </c>
       <c r="T15" s="19">
         <v>1</v>
       </c>
-      <c r="U15" s="32">
+      <c r="U15" s="25">
         <v>11137</v>
       </c>
+      <c r="V15" s="2">
+        <v>1</v>
+      </c>
+      <c r="W15" s="27">
+        <v>1</v>
+      </c>
+      <c r="X15" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="25">
+        <v>12716</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="19">
+        <v>0.83333333333333304</v>
+      </c>
+      <c r="AC15" s="25">
+        <v>13405</v>
+      </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2">
         <v>1</v>
       </c>
-      <c r="E16" s="34">
-        <v>1</v>
-      </c>
-      <c r="F16" s="34">
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
         <v>1</v>
       </c>
       <c r="G16" s="18">
         <v>12286</v>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="25">
         <v>1</v>
       </c>
       <c r="I16" s="2">
         <v>0.8</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="27">
         <v>0.88888888888888795</v>
       </c>
       <c r="K16" s="3">
         <v>1</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="25">
         <v>7657</v>
       </c>
       <c r="M16" s="2">
         <v>0.90909090909090895</v>
       </c>
-      <c r="N16" s="34">
+      <c r="N16" s="27">
         <v>1</v>
       </c>
       <c r="O16" s="3">
         <v>0.75</v>
       </c>
-      <c r="P16" s="31">
+      <c r="P16">
         <v>19745</v>
       </c>
-      <c r="Q16" s="32">
+      <c r="Q16" s="25">
         <v>2</v>
       </c>
       <c r="R16" s="2">
         <v>1</v>
       </c>
-      <c r="S16" s="34">
+      <c r="S16" s="27">
         <v>1</v>
       </c>
       <c r="T16" s="19">
         <v>1</v>
       </c>
-      <c r="U16" s="32">
+      <c r="U16" s="25">
         <v>9236</v>
       </c>
+      <c r="V16" s="2">
+        <v>1</v>
+      </c>
+      <c r="W16" s="27">
+        <v>1</v>
+      </c>
+      <c r="X16" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="25">
+        <v>11368</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="27">
+        <v>0.94117647058823495</v>
+      </c>
+      <c r="AB16" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="25">
+        <v>10431</v>
+      </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A17" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -8415,7 +8878,7 @@
       <c r="G17" s="20">
         <v>14865</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="34">
         <v>1</v>
       </c>
       <c r="I17" s="4">
@@ -8427,7 +8890,7 @@
       <c r="K17" s="6">
         <v>1</v>
       </c>
-      <c r="L17" s="42">
+      <c r="L17" s="34">
         <v>10115</v>
       </c>
       <c r="M17" s="4">
@@ -8442,7 +8905,7 @@
       <c r="P17" s="21">
         <v>12597</v>
       </c>
-      <c r="Q17" s="42">
+      <c r="Q17" s="34">
         <v>1</v>
       </c>
       <c r="R17" s="4">
@@ -8454,19 +8917,43 @@
       <c r="T17" s="22">
         <v>1</v>
       </c>
-      <c r="U17" s="42">
+      <c r="U17" s="34">
         <v>9107</v>
       </c>
+      <c r="V17" s="4">
+        <v>1</v>
+      </c>
+      <c r="W17" s="5">
+        <v>1</v>
+      </c>
+      <c r="X17" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="34">
+        <v>11539</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="34">
+        <v>12026</v>
+      </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
@@ -8522,211 +9009,307 @@
       <c r="U18" s="12">
         <v>11146</v>
       </c>
+      <c r="V18" s="14">
+        <v>1</v>
+      </c>
+      <c r="W18" s="15">
+        <v>1</v>
+      </c>
+      <c r="X18" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="12">
+        <v>11270</v>
+      </c>
+      <c r="Z18" s="14">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="15">
+        <v>0.92857142857142805</v>
+      </c>
+      <c r="AB18" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="12">
+        <v>11520</v>
+      </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="2">
         <v>0.9375</v>
       </c>
-      <c r="E19" s="34">
+      <c r="E19" s="27">
         <v>0.94117647058823495</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="27">
         <v>1</v>
       </c>
       <c r="G19" s="18">
         <v>19259</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="25">
         <v>2</v>
       </c>
       <c r="I19" s="2">
         <v>1</v>
       </c>
-      <c r="J19" s="34">
+      <c r="J19" s="27">
         <v>0.64285714285714202</v>
       </c>
       <c r="K19" s="3">
         <v>1</v>
       </c>
-      <c r="L19" s="32">
+      <c r="L19" s="25">
         <v>7462</v>
       </c>
       <c r="M19" s="2">
         <v>0.8</v>
       </c>
-      <c r="N19" s="34">
+      <c r="N19" s="27">
         <v>1</v>
       </c>
       <c r="O19" s="3">
         <v>1</v>
       </c>
-      <c r="P19" s="31">
+      <c r="P19">
         <v>13229</v>
       </c>
-      <c r="Q19" s="32">
+      <c r="Q19" s="25">
         <v>1</v>
       </c>
       <c r="R19" s="2">
         <v>1</v>
       </c>
-      <c r="S19" s="34">
+      <c r="S19" s="27">
         <v>1</v>
       </c>
       <c r="T19" s="19">
         <v>1</v>
       </c>
-      <c r="U19" s="32">
+      <c r="U19" s="25">
         <v>7916</v>
       </c>
+      <c r="V19" s="2">
+        <v>1</v>
+      </c>
+      <c r="W19" s="27">
+        <v>1</v>
+      </c>
+      <c r="X19" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="25">
+        <v>8714</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="AA19" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="25">
+        <v>10540</v>
+      </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A20" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20" s="2">
         <v>0.91666666666666596</v>
       </c>
-      <c r="E20" s="34">
-        <v>1</v>
-      </c>
-      <c r="F20" s="34">
+      <c r="E20" s="27">
+        <v>1</v>
+      </c>
+      <c r="F20" s="27">
         <v>0.75</v>
       </c>
       <c r="G20" s="18">
         <v>13615</v>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="25">
         <v>1</v>
       </c>
       <c r="I20" s="2">
         <v>1</v>
       </c>
-      <c r="J20" s="34">
+      <c r="J20" s="27">
         <v>1</v>
       </c>
       <c r="K20" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="L20" s="32">
+      <c r="L20" s="25">
         <v>8820</v>
       </c>
       <c r="M20" s="2">
         <v>1</v>
       </c>
-      <c r="N20" s="34">
+      <c r="N20" s="27">
         <v>1</v>
       </c>
       <c r="O20" s="3">
         <v>0.66666666666666596</v>
       </c>
-      <c r="P20" s="31">
+      <c r="P20">
         <v>13562</v>
       </c>
-      <c r="Q20" s="32">
+      <c r="Q20" s="25">
         <v>1</v>
       </c>
       <c r="R20" s="2">
         <v>1</v>
       </c>
-      <c r="S20" s="34">
+      <c r="S20" s="27">
         <v>1</v>
       </c>
       <c r="T20" s="19">
         <v>1</v>
       </c>
-      <c r="U20" s="32">
+      <c r="U20" s="25">
         <v>9736</v>
       </c>
+      <c r="V20" s="2">
+        <v>1</v>
+      </c>
+      <c r="W20" s="27">
+        <v>0.91666666666666596</v>
+      </c>
+      <c r="X20" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="25">
+        <v>10988</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="25">
+        <v>10883</v>
+      </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D21" s="2">
         <v>0.94444444444444398</v>
       </c>
-      <c r="E21" s="34">
-        <v>1</v>
-      </c>
-      <c r="F21" s="34">
+      <c r="E21" s="27">
+        <v>1</v>
+      </c>
+      <c r="F21" s="27">
         <v>1</v>
       </c>
       <c r="G21" s="18">
         <v>13440</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="25">
         <v>1</v>
       </c>
       <c r="I21" s="2">
         <v>1</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J21" s="27">
         <v>1</v>
       </c>
       <c r="K21" s="3">
         <v>1</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="25">
         <v>10773</v>
       </c>
       <c r="M21" s="2">
         <v>1</v>
       </c>
-      <c r="N21" s="34">
+      <c r="N21" s="27">
         <v>1</v>
       </c>
       <c r="O21" s="3">
         <v>1</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21">
         <v>13796</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="25">
         <v>1</v>
       </c>
       <c r="R21" s="2">
         <v>0.90909090909090895</v>
       </c>
-      <c r="S21" s="34">
+      <c r="S21" s="27">
         <v>1</v>
       </c>
       <c r="T21" s="19">
         <v>1</v>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="25">
         <v>11661</v>
       </c>
+      <c r="V21" s="2">
+        <v>1</v>
+      </c>
+      <c r="W21" s="27">
+        <v>1</v>
+      </c>
+      <c r="X21" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="25">
+        <v>12074</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0.86666666666666603</v>
+      </c>
+      <c r="AA21" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="25">
+        <v>11693</v>
+      </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A22" s="20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
@@ -8740,7 +9323,7 @@
       <c r="G22" s="20">
         <v>18272</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="34">
         <v>1</v>
       </c>
       <c r="I22" s="4">
@@ -8752,7 +9335,7 @@
       <c r="K22" s="6">
         <v>0.8</v>
       </c>
-      <c r="L22" s="42">
+      <c r="L22" s="34">
         <v>11688</v>
       </c>
       <c r="M22" s="4">
@@ -8767,7 +9350,7 @@
       <c r="P22" s="21">
         <v>15634</v>
       </c>
-      <c r="Q22" s="42">
+      <c r="Q22" s="34">
         <v>1</v>
       </c>
       <c r="R22" s="4">
@@ -8779,19 +9362,43 @@
       <c r="T22" s="22">
         <v>1</v>
       </c>
-      <c r="U22" s="42">
+      <c r="U22" s="34">
         <v>13004</v>
       </c>
+      <c r="V22" s="4">
+        <v>1</v>
+      </c>
+      <c r="W22" s="5">
+        <v>0.88888888888888795</v>
+      </c>
+      <c r="X22" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="34">
+        <v>13103</v>
+      </c>
+      <c r="Z22" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="34">
+        <v>13019</v>
+      </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
@@ -8805,7 +9412,7 @@
       <c r="G23" s="18">
         <v>24554</v>
       </c>
-      <c r="H23" s="32">
+      <c r="H23" s="25">
         <v>2</v>
       </c>
       <c r="I23" s="14">
@@ -8817,7 +9424,7 @@
       <c r="K23" s="16">
         <v>1</v>
       </c>
-      <c r="L23" s="32">
+      <c r="L23" s="25">
         <v>11381</v>
       </c>
       <c r="M23" s="14">
@@ -8829,10 +9436,10 @@
       <c r="O23" s="16">
         <v>1</v>
       </c>
-      <c r="P23" s="31">
+      <c r="P23">
         <v>17382</v>
       </c>
-      <c r="Q23" s="32">
+      <c r="Q23" s="25">
         <v>1</v>
       </c>
       <c r="R23" s="14">
@@ -8844,214 +9451,310 @@
       <c r="T23" s="17">
         <v>1</v>
       </c>
-      <c r="U23" s="32">
+      <c r="U23" s="25">
         <v>12326</v>
       </c>
+      <c r="V23" s="14">
+        <v>1</v>
+      </c>
+      <c r="W23" s="15">
+        <v>1</v>
+      </c>
+      <c r="X23" s="17">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="25">
+        <v>14817</v>
+      </c>
+      <c r="Z23" s="14">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="15">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="17">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="25">
+        <v>13156</v>
+      </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D24" s="2">
         <v>0.86666666666666603</v>
       </c>
-      <c r="E24" s="34">
+      <c r="E24" s="27">
         <v>0.95</v>
       </c>
-      <c r="F24" s="34">
+      <c r="F24" s="27">
         <v>1</v>
       </c>
       <c r="G24" s="18">
         <v>15578</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="25">
         <v>1</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
       </c>
-      <c r="J24" s="34">
+      <c r="J24" s="27">
         <v>1</v>
       </c>
       <c r="K24" s="3">
         <v>1</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="25">
         <v>11651</v>
       </c>
       <c r="M24" s="2">
         <v>1</v>
       </c>
-      <c r="N24" s="34">
+      <c r="N24" s="27">
         <v>1</v>
       </c>
       <c r="O24" s="3">
         <v>1</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24">
         <v>18017</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="25">
         <v>1</v>
       </c>
       <c r="R24" s="2">
         <v>1</v>
       </c>
-      <c r="S24" s="34">
+      <c r="S24" s="27">
         <v>0.95454545454545403</v>
       </c>
       <c r="T24" s="19">
         <v>1</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="25">
         <v>11941</v>
       </c>
+      <c r="V24" s="2">
+        <v>1</v>
+      </c>
+      <c r="W24" s="27">
+        <v>0.952380952380952</v>
+      </c>
+      <c r="X24" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="25">
+        <v>15939</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>0.94736842105263097</v>
+      </c>
+      <c r="AA24" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="25">
+        <v>13296</v>
+      </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A25" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D25" s="2">
         <v>1</v>
       </c>
-      <c r="E25" s="34">
+      <c r="E25" s="27">
         <v>0.94736842105263097</v>
       </c>
-      <c r="F25" s="34">
+      <c r="F25" s="27">
         <v>1</v>
       </c>
       <c r="G25" s="18">
         <v>18393</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="25">
         <v>1</v>
       </c>
       <c r="I25" s="2">
         <v>1</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J25" s="27">
         <v>1</v>
       </c>
       <c r="K25" s="3">
         <v>1</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="25">
         <v>11710</v>
       </c>
       <c r="M25" s="2">
         <v>1</v>
       </c>
-      <c r="N25" s="34">
+      <c r="N25" s="27">
         <v>1</v>
       </c>
       <c r="O25" s="3">
         <v>1</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25">
         <v>30484</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="25">
         <v>2</v>
       </c>
       <c r="R25" s="2">
         <v>1</v>
       </c>
-      <c r="S25" s="34">
+      <c r="S25" s="27">
         <v>1</v>
       </c>
       <c r="T25" s="19">
         <v>1</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="25">
         <v>11743</v>
       </c>
+      <c r="V25" s="2">
+        <v>1</v>
+      </c>
+      <c r="W25" s="27">
+        <v>1</v>
+      </c>
+      <c r="X25" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="25">
+        <v>14297</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="25">
+        <v>14864</v>
+      </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D26" s="2">
         <v>1</v>
       </c>
-      <c r="E26" s="34">
-        <v>1</v>
-      </c>
-      <c r="F26" s="34">
+      <c r="E26" s="27">
+        <v>1</v>
+      </c>
+      <c r="F26" s="27">
         <v>1</v>
       </c>
       <c r="G26" s="18">
         <v>18983</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="25">
         <v>1</v>
       </c>
       <c r="I26" s="2">
         <v>1</v>
       </c>
-      <c r="J26" s="34">
+      <c r="J26" s="27">
         <v>1</v>
       </c>
       <c r="K26" s="3">
         <v>1</v>
       </c>
-      <c r="L26" s="32">
+      <c r="L26" s="25">
         <v>10891</v>
       </c>
       <c r="M26" s="2">
         <v>1</v>
       </c>
-      <c r="N26" s="34">
+      <c r="N26" s="27">
         <v>1</v>
       </c>
       <c r="O26" s="3">
         <v>0.85714285714285698</v>
       </c>
-      <c r="P26" s="31">
+      <c r="P26">
         <v>20151</v>
       </c>
-      <c r="Q26" s="32">
+      <c r="Q26" s="25">
         <v>1</v>
       </c>
       <c r="R26" s="2">
         <v>1</v>
       </c>
-      <c r="S26" s="34">
+      <c r="S26" s="27">
         <v>1</v>
       </c>
       <c r="T26" s="19">
         <v>1</v>
       </c>
-      <c r="U26" s="32">
+      <c r="U26" s="25">
         <v>13002</v>
       </c>
+      <c r="V26" s="2">
+        <v>1</v>
+      </c>
+      <c r="W26" s="27">
+        <v>0.96</v>
+      </c>
+      <c r="X26" s="19">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="25">
+        <v>15466</v>
+      </c>
+      <c r="Z26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="27">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="19">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="25">
+        <v>13711</v>
+      </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
       <c r="A27" s="20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D27" s="4">
         <v>0.86666666666666603</v>
@@ -9065,7 +9768,7 @@
       <c r="G27" s="18">
         <v>17457</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="25">
         <v>1</v>
       </c>
       <c r="I27" s="4">
@@ -9077,7 +9780,7 @@
       <c r="K27" s="6">
         <v>1</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="25">
         <v>12779</v>
       </c>
       <c r="M27" s="4">
@@ -9089,10 +9792,10 @@
       <c r="O27" s="6">
         <v>1</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27">
         <v>17201</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="25">
         <v>1</v>
       </c>
       <c r="R27" s="4">
@@ -9104,67 +9807,91 @@
       <c r="T27" s="22">
         <v>1</v>
       </c>
-      <c r="U27" s="32">
+      <c r="U27" s="25">
         <v>12517</v>
       </c>
+      <c r="V27" s="4">
+        <v>0.94444444444444398</v>
+      </c>
+      <c r="W27" s="5">
+        <v>1</v>
+      </c>
+      <c r="X27" s="22">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="25">
+        <v>14952</v>
+      </c>
+      <c r="Z27" s="4">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="5">
+        <v>0.95454545454545403</v>
+      </c>
+      <c r="AB27" s="22">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="25">
+        <v>15121</v>
+      </c>
     </row>
-    <row r="28" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C28" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D28" s="7">
         <f>AVERAGE(D3:D27)</f>
         <v>0.97204700854700843</v>
       </c>
       <c r="E28" s="8">
-        <f t="shared" ref="E28:G28" si="0">AVERAGE(E3:E27)</f>
+        <f t="shared" ref="E28" si="0">AVERAGE(E3:E27)</f>
         <v>0.98721431028551765</v>
       </c>
       <c r="F28" s="8">
         <f>AVERAGE(F3:F27)</f>
         <v>0.96666666666666656</v>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="33">
         <f>AVERAGE(G3:G27)</f>
         <v>16870.72</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="26">
         <f>COUNTIF(H3:H27,2)</f>
         <v>6</v>
       </c>
       <c r="I28" s="7">
-        <f>AVERAGE(I3:I27)</f>
+        <f t="shared" ref="I28:P28" si="1">AVERAGE(I3:I27)</f>
         <v>0.98533333333333328</v>
       </c>
       <c r="J28" s="8">
-        <f>AVERAGE(J3:J27)</f>
+        <f t="shared" si="1"/>
         <v>0.96231846229928053</v>
       </c>
       <c r="K28" s="9">
-        <f>AVERAGE(K3:K27)</f>
+        <f t="shared" si="1"/>
         <v>0.90866666666666662</v>
       </c>
-      <c r="L28" s="41">
-        <f>AVERAGE(L3:L27)</f>
+      <c r="L28" s="33">
+        <f t="shared" si="1"/>
         <v>10250.719999999999</v>
       </c>
       <c r="M28" s="7">
-        <f>AVERAGE(M3:M27)</f>
+        <f t="shared" si="1"/>
         <v>0.98601069518716566</v>
       </c>
       <c r="N28" s="8">
-        <f>AVERAGE(N3:N27)</f>
+        <f t="shared" si="1"/>
         <v>0.98141251791686568</v>
       </c>
       <c r="O28" s="9">
-        <f>AVERAGE(O3:O27)</f>
+        <f t="shared" si="1"/>
         <v>0.88470995670995667</v>
       </c>
-      <c r="P28" s="41">
-        <f>AVERAGE(P3:P27)</f>
+      <c r="P28" s="33">
+        <f t="shared" si="1"/>
         <v>16484.48</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="26">
         <f>COUNTIF(Q3:Q27,2)</f>
         <v>3</v>
       </c>
@@ -9180,94 +9907,162 @@
         <f>AVERAGE(T3:T27)</f>
         <v>0.97333333333333327</v>
       </c>
-      <c r="U28" s="41">
+      <c r="U28" s="33">
         <f>AVERAGE(U3:U27)</f>
         <v>10966.28</v>
       </c>
+      <c r="V28" s="7">
+        <f>AVERAGE(V3:V27)</f>
+        <v>0.98959150326797385</v>
+      </c>
+      <c r="W28" s="8">
+        <f>AVERAGE(W3:W27)</f>
+        <v>0.98738412698412692</v>
+      </c>
+      <c r="X28" s="9">
+        <f>AVERAGE(X3:X27)</f>
+        <v>0.92</v>
+      </c>
+      <c r="Y28" s="33">
+        <f>AVERAGE(Y3:Y27)</f>
+        <v>12224.56</v>
+      </c>
+      <c r="Z28" s="7">
+        <f>AVERAGE(Z3:Z27)</f>
+        <v>0.9822084623323013</v>
+      </c>
+      <c r="AA28" s="8">
+        <f>AVERAGE(AA3:AA27)</f>
+        <v>0.96244210124241081</v>
+      </c>
+      <c r="AB28" s="9">
+        <f>AVERAGE(AB3:AB27)</f>
+        <v>0.91266666666666663</v>
+      </c>
+      <c r="AC28" s="33">
+        <f>AVERAGE(AC3:AC27)</f>
+        <v>12087.56</v>
+      </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
       <c r="C29" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="36">
+        <v>48</v>
+      </c>
+      <c r="D29" s="28">
         <f>25-COUNTIF(D3:D27,1)</f>
         <v>6</v>
       </c>
-      <c r="E29" s="37">
-        <f t="shared" ref="E29:F29" si="1">25-COUNTIF(E3:E27,1)</f>
+      <c r="E29" s="29">
+        <f t="shared" ref="E29:F29" si="2">25-COUNTIF(E3:E27,1)</f>
         <v>6</v>
       </c>
-      <c r="F29" s="38">
-        <f t="shared" si="1"/>
+      <c r="F29" s="30">
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="I29" s="36">
+      <c r="I29" s="28">
         <f>25-COUNTIF(I3:I27,1)</f>
         <v>3</v>
       </c>
-      <c r="J29" s="37">
-        <f t="shared" ref="J29:K29" si="2">25-COUNTIF(J3:J27,1)</f>
+      <c r="J29" s="29">
+        <f t="shared" ref="J29:K29" si="3">25-COUNTIF(J3:J27,1)</f>
         <v>8</v>
       </c>
-      <c r="K29" s="38">
-        <f t="shared" si="2"/>
+      <c r="K29" s="30">
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="M29" s="36">
+      <c r="M29" s="28">
         <f>25-COUNTIF(M3:M27,1)</f>
         <v>3</v>
       </c>
-      <c r="N29" s="37">
-        <f t="shared" ref="N29:O29" si="3">25-COUNTIF(N3:N27,1)</f>
+      <c r="N29" s="29">
+        <f t="shared" ref="N29:O29" si="4">25-COUNTIF(N3:N27,1)</f>
         <v>6</v>
       </c>
-      <c r="O29" s="38">
-        <f t="shared" si="3"/>
+      <c r="O29" s="30">
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="R29" s="36">
+      <c r="R29" s="28">
         <f>25-COUNTIF(R3:R27,1)</f>
         <v>3</v>
       </c>
-      <c r="S29" s="37">
-        <f t="shared" ref="S29:T29" si="4">25-COUNTIF(S3:S27,1)</f>
+      <c r="S29" s="29">
+        <f t="shared" ref="S29:T29" si="5">25-COUNTIF(S3:S27,1)</f>
         <v>6</v>
       </c>
-      <c r="T29" s="38">
-        <f t="shared" si="4"/>
+      <c r="T29" s="30">
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
+      <c r="V29" s="28">
+        <f>25-COUNTIF(V3:V27,1)</f>
+        <v>4</v>
+      </c>
+      <c r="W29" s="29">
+        <f t="shared" ref="W29:X29" si="6">25-COUNTIF(W3:W27,1)</f>
+        <v>5</v>
+      </c>
+      <c r="X29" s="30">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="Z29" s="28">
+        <f>25-COUNTIF(Z3:Z27,1)</f>
+        <v>4</v>
+      </c>
+      <c r="AA29" s="29">
+        <f t="shared" ref="AA29:AB29" si="7">25-COUNTIF(AA3:AA27,1)</f>
+        <v>7</v>
+      </c>
+      <c r="AB29" s="30">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
       <c r="C30" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="28">
+        <v>49</v>
+      </c>
+      <c r="D30" s="35">
         <f>AVERAGE(D29:F29)</f>
         <v>5</v>
       </c>
-      <c r="E30" s="29"/>
-      <c r="F30" s="30"/>
-      <c r="I30" s="28">
+      <c r="E30" s="36"/>
+      <c r="F30" s="37"/>
+      <c r="I30" s="35">
         <f>AVERAGE(I29:K29)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="J30" s="29"/>
-      <c r="K30" s="30"/>
-      <c r="M30" s="28">
+      <c r="J30" s="36"/>
+      <c r="K30" s="37"/>
+      <c r="M30" s="35">
         <f>AVERAGE(M29:O29)</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="N30" s="29"/>
-      <c r="O30" s="30"/>
-      <c r="R30" s="28">
+      <c r="N30" s="36"/>
+      <c r="O30" s="37"/>
+      <c r="R30" s="35">
         <f>AVERAGE(R29:T29)</f>
         <v>3.6666666666666665</v>
       </c>
-      <c r="S30" s="29"/>
-      <c r="T30" s="30"/>
+      <c r="S30" s="36"/>
+      <c r="T30" s="37"/>
+      <c r="V30" s="35">
+        <f>AVERAGE(V29:X29)</f>
+        <v>4</v>
+      </c>
+      <c r="W30" s="36"/>
+      <c r="X30" s="37"/>
+      <c r="Z30" s="35">
+        <f>AVERAGE(Z29:AB29)</f>
+        <v>5.333333333333333</v>
+      </c>
+      <c r="AA30" s="36"/>
+      <c r="AB30" s="37"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
       <c r="G31">
         <f>SUM(G3:G27)</f>
         <v>421768</v>
@@ -9284,9 +10079,21 @@
         <f>SUM(U3:U27)</f>
         <v>274157</v>
       </c>
+      <c r="Y31">
+        <f>SUM(Y3:Y27)</f>
+        <v>305614</v>
+      </c>
+      <c r="AC31">
+        <f>SUM(AC3:AC27)</f>
+        <v>302189</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="12">
+    <mergeCell ref="V1:Y1"/>
+    <mergeCell ref="V30:X30"/>
+    <mergeCell ref="Z1:AC1"/>
+    <mergeCell ref="Z30:AB30"/>
     <mergeCell ref="M30:O30"/>
     <mergeCell ref="I30:K30"/>
     <mergeCell ref="R30:T30"/>
@@ -9296,8 +10103,72 @@
     <mergeCell ref="R1:U1"/>
     <mergeCell ref="D30:F30"/>
   </mergeCells>
+  <conditionalFormatting sqref="G3:G27 L3:L27 P3:P27 U3:U27">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G27">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H3:H27 Q3:Q27">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L3:L27">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L28 G28 P28 U28">
+    <cfRule type="dataBar" priority="19">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8DBD9729-F9A2-4FD1-B0AB-CF3111D1A845}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P3:P27">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="R3:T28 I3:K28 D3:F28 M3:O28">
-    <cfRule type="colorScale" priority="32">
+    <cfRule type="colorScale" priority="46">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9309,7 +10180,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R28:T28 I28:K28 D28:F28 M28:O28">
-    <cfRule type="colorScale" priority="37">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -9321,7 +10192,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R29:T29 I29:K29 D29:F29 M29:O29">
-    <cfRule type="dataBar" priority="42">
+    <cfRule type="dataBar" priority="56">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9334,8 +10205,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G27 L3:L27 P3:P27 U3:U27">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="U3:U27">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9344,8 +10215,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H3:H27 Q3:Q27">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="Y3:Y27">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9354,8 +10225,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L28 G28 P28 U28">
-    <cfRule type="dataBar" priority="5">
+  <conditionalFormatting sqref="Y28">
+    <cfRule type="dataBar" priority="10">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9363,13 +10234,51 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{8DBD9729-F9A2-4FD1-B0AB-CF3111D1A845}</x14:id>
+          <x14:id>{FBEA4B46-FDAB-4742-A972-792D951C4FF3}</x14:id>
         </ext>
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:G27">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="V3:X28">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V28:X28">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V29:X29">
+    <cfRule type="dataBar" priority="14">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{9803B8BC-4E53-4E35-A633-7F1F36489D26}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y3:Y27">
+    <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -9378,7 +10287,69 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:L27">
+  <conditionalFormatting sqref="AC3:AC27">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC28">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{8FF26D4A-4A91-41EA-B253-262B4BADDC7D}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z3:AB28">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z28:AB28">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z29:AB29">
+    <cfRule type="dataBar" priority="8">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C2BC76FE-3583-423F-98E5-2B196EEABA7C}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC3:AC27">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -9388,24 +10359,32 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P27">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
+  <conditionalFormatting sqref="G28 L28 P28 U28 AC28">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{03452ECF-DADF-4CDD-99D0-8717F23793BD}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U3:U27">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
+  <conditionalFormatting sqref="L28 G28 P28 U28 AC28 Y28">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C287B8E9-D1A1-43C9-8633-268AA5482846}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9413,6 +10392,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8DBD9729-F9A2-4FD1-B0AB-CF3111D1A845}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L28 G28 P28 U28</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1CBD6AED-E61C-4CA0-8210-5EA7351ABED4}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
@@ -9427,7 +10419,7 @@
           <xm:sqref>R29:T29 I29:K29 D29:F29 M29:O29</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{8DBD9729-F9A2-4FD1-B0AB-CF3111D1A845}">
+          <x14:cfRule type="dataBar" id="{FBEA4B46-FDAB-4742-A972-792D951C4FF3}">
             <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -9437,7 +10429,72 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>L28 G28 P28 U28</xm:sqref>
+          <xm:sqref>Y28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{9803B8BC-4E53-4E35-A633-7F1F36489D26}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>V29:X29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{8FF26D4A-4A91-41EA-B253-262B4BADDC7D}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AC28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C2BC76FE-3583-423F-98E5-2B196EEABA7C}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>Z29:AB29</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{03452ECF-DADF-4CDD-99D0-8717F23793BD}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G28 L28 P28 U28 AC28</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C287B8E9-D1A1-43C9-8633-268AA5482846}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>L28 G28 P28 U28 AC28 Y28</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
